--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johan\monitor-ingresos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4343" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4730" uniqueCount="845">
   <si>
     <t>ID PDV</t>
   </si>
@@ -2289,6 +2289,276 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1090436828_DBD_INGRESO_PDV_35217_23_09_2026_09_00_21.jpg</t>
+  </si>
+  <si>
+    <t>7824689</t>
+  </si>
+  <si>
+    <t>4.891917916666667</t>
+  </si>
+  <si>
+    <t>-74.03327221666667</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:03:00</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1075688960_DBD_INGRESO_PDV_10772_23_09_2026_09_02_59.jpg</t>
+  </si>
+  <si>
+    <t>7824690</t>
+  </si>
+  <si>
+    <t>10.948503333333333</t>
+  </si>
+  <si>
+    <t>-74.78309666666668</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:03:04</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/72098375_DBD_INGRESO_PDV_2638_23_09_2026_09_03_02.jpg</t>
+  </si>
+  <si>
+    <t>7824692</t>
+  </si>
+  <si>
+    <t>4.678341666666666</t>
+  </si>
+  <si>
+    <t>-74.11810999999999</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:03:51</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/80115103_DBD_INGRESO_PDV_22870_23_09_2026_09_03_50.jpg</t>
+  </si>
+  <si>
+    <t>7824694</t>
+  </si>
+  <si>
+    <t>11.225459999999998</t>
+  </si>
+  <si>
+    <t>-74.174025</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:05:22</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1110533250_DBD_INGRESO_PDV_23897_23_09_2026_09_05_21.jpg</t>
+  </si>
+  <si>
+    <t>7824700</t>
+  </si>
+  <si>
+    <t>10.383586666666668</t>
+  </si>
+  <si>
+    <t>-75.46936166666666</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:08:44</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1002247264_DBD_INGRESO_PDV_8379_23_09_2026_09_08_43.jpg</t>
+  </si>
+  <si>
+    <t>7824703</t>
+  </si>
+  <si>
+    <t>4.6848443</t>
+  </si>
+  <si>
+    <t>-74.0790118</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:11:16</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1028865500_DBD_INGRESO_PDV_59330_23_09_2026_09_11_16.jpg</t>
+  </si>
+  <si>
+    <t>7824709</t>
+  </si>
+  <si>
+    <t>7.1154159</t>
+  </si>
+  <si>
+    <t>-73.1202411</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:17:30</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1102716954_DBD_INGRESO_PDV_80680_23_09_2026_09_17_30.jpg</t>
+  </si>
+  <si>
+    <t>7824721</t>
+  </si>
+  <si>
+    <t>4.588721666666667</t>
+  </si>
+  <si>
+    <t>-74.20568666666667</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:27:10</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1014305216_DBD_INGRESO_PDV_79821_23_09_2026_09_27_10.jpg</t>
+  </si>
+  <si>
+    <t>7824731</t>
+  </si>
+  <si>
+    <t>6.1776837</t>
+  </si>
+  <si>
+    <t>-75.5911041</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:32:15</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/71780913_DBD_INGRESO_PDV_30515_23_09_2026_09_32_06.jpg</t>
+  </si>
+  <si>
+    <t>7824732</t>
+  </si>
+  <si>
+    <t>3.3698833594098687</t>
+  </si>
+  <si>
+    <t>-76.5263925679028</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:33:27</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1114813506_DBD_INGRESO_PDV_81696_23_09_2026_09_33_26.jpg</t>
+  </si>
+  <si>
+    <t>7824740</t>
+  </si>
+  <si>
+    <t>3.4726799999999995</t>
+  </si>
+  <si>
+    <t>-76.52827</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:38:15</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/94412336_DBD_INGRESO_PDV_48560_23_09_2026_09_38_15.jpg</t>
+  </si>
+  <si>
+    <t>7824743</t>
+  </si>
+  <si>
+    <t>6.24955507</t>
+  </si>
+  <si>
+    <t>-75.58426619</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:39:53</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1007634699_DBD_INGRESO_PDV_22864_23_09_2026_09_39_51.jpg</t>
+  </si>
+  <si>
+    <t>7824768</t>
+  </si>
+  <si>
+    <t>10.493436666666666</t>
+  </si>
+  <si>
+    <t>-73.26734</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:52:03</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1065626573_DBD_INGRESO_PDV_85091_23_09_2026_09_52_01.jpg</t>
+  </si>
+  <si>
+    <t>7824775</t>
+  </si>
+  <si>
+    <t>4.700948</t>
+  </si>
+  <si>
+    <t>-74.2307263</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:57:30</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1070464010_DBD_INGRESO_PDV_71439_23_09_2026_09_57_29.jpg</t>
+  </si>
+  <si>
+    <t>7824780</t>
+  </si>
+  <si>
+    <t>11.015293333333334</t>
+  </si>
+  <si>
+    <t>-74.82933166666666</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:58:48</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/72257237_DBD_INGRESO_PDV_46344_23_09_2026_09_58_47.jpg</t>
+  </si>
+  <si>
+    <t>7824781</t>
+  </si>
+  <si>
+    <t>4.618398333333333</t>
+  </si>
+  <si>
+    <t>-74.08616833333333</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:59:26</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1233490257_DBD_INGRESO_PDV_5747_23_09_2026_09_59_24.jpg</t>
+  </si>
+  <si>
+    <t>7824926</t>
+  </si>
+  <si>
+    <t>4.7303521</t>
+  </si>
+  <si>
+    <t>-74.0329322</t>
+  </si>
+  <si>
+    <t>23/09/2026 11:04:10</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/11225449_DBD_INGRESO_PDV_71086_23_09_2026_11_04_09.jpg</t>
+  </si>
+  <si>
+    <t>7824935</t>
+  </si>
+  <si>
+    <t>6.250681666666666</t>
+  </si>
+  <si>
+    <t>-75.583835</t>
+  </si>
+  <si>
+    <t>23/09/2026 11:06:42</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1035227940_DBD_INGRESO_PDV_81723_23_09_2026_11_06_40.jpg</t>
   </si>
 </sst>
 </file>
@@ -12996,7 +13266,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG43"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -15971,7 +16241,7 @@
       </c>
       <c r="AG36" s="2"/>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>719</v>
       </c>
@@ -15993,10 +16263,6 @@
       <c r="G37" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
       <c r="L37" s="3" t="s">
         <v>123</v>
       </c>
@@ -16027,16 +16293,9 @@
       <c r="U37" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
       <c r="Z37" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="AA37" s="3"/>
-      <c r="AB37" s="3"/>
-      <c r="AC37" s="3"/>
       <c r="AD37" s="3" t="s">
         <v>723</v>
       </c>
@@ -16046,16 +16305,14 @@
       <c r="AF37" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AG37" s="3"/>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>724</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C38" s="3"/>
       <c r="D38" s="3" t="s">
         <v>208</v>
       </c>
@@ -16068,11 +16325,6 @@
       <c r="G38" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
         <v>34</v>
       </c>
@@ -16100,16 +16352,9 @@
       <c r="U38" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
       <c r="Z38" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="AA38" s="3"/>
-      <c r="AB38" s="3"/>
-      <c r="AC38" s="3"/>
       <c r="AD38" s="3" t="s">
         <v>729</v>
       </c>
@@ -16123,7 +16368,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>730</v>
       </c>
@@ -16145,10 +16390,6 @@
       <c r="G39" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
         <v>123</v>
       </c>
@@ -16179,16 +16420,9 @@
       <c r="U39" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
       <c r="Z39" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="AA39" s="3"/>
-      <c r="AB39" s="3"/>
-      <c r="AC39" s="3"/>
       <c r="AD39" s="3" t="s">
         <v>734</v>
       </c>
@@ -16202,7 +16436,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>735</v>
       </c>
@@ -16224,10 +16458,6 @@
       <c r="G40" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
         <v>123</v>
       </c>
@@ -16258,16 +16488,9 @@
       <c r="U40" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
       <c r="Z40" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="AA40" s="3"/>
-      <c r="AB40" s="3"/>
-      <c r="AC40" s="3"/>
       <c r="AD40" s="3" t="s">
         <v>739</v>
       </c>
@@ -16277,9 +16500,8 @@
       <c r="AF40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>740</v>
       </c>
@@ -16301,10 +16523,6 @@
       <c r="G41" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
       <c r="L41" s="3" t="s">
         <v>123</v>
       </c>
@@ -16335,16 +16553,9 @@
       <c r="U41" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
       <c r="Z41" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="AA41" s="3"/>
-      <c r="AB41" s="3"/>
-      <c r="AC41" s="3"/>
       <c r="AD41" s="3" t="s">
         <v>744</v>
       </c>
@@ -16358,7 +16569,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>745</v>
       </c>
@@ -16380,10 +16591,6 @@
       <c r="G42" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
       <c r="L42" s="3" t="s">
         <v>123</v>
       </c>
@@ -16414,16 +16621,9 @@
       <c r="U42" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
       <c r="Z42" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="AA42" s="3"/>
-      <c r="AB42" s="3"/>
-      <c r="AC42" s="3"/>
       <c r="AD42" s="3" t="s">
         <v>749</v>
       </c>
@@ -16437,7 +16637,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>750</v>
       </c>
@@ -16459,10 +16659,6 @@
       <c r="G43" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
       <c r="L43" s="3" t="s">
         <v>123</v>
       </c>
@@ -16493,16 +16689,9 @@
       <c r="U43" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
       <c r="Z43" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="AA43" s="3"/>
-      <c r="AB43" s="3"/>
-      <c r="AC43" s="3"/>
       <c r="AD43" s="3" t="s">
         <v>754</v>
       </c>
@@ -16512,7 +16701,1203 @@
       <c r="AF43" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AG43" s="3"/>
+    </row>
+    <row r="44" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG44" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD46" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="AE46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="AE47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG47" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD49" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF49" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T50" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="U50" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z50" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD50" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="AE50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG50" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T51" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="U51" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z51" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD51" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="AE51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG51" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="S53" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T53" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="U53" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z53" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD53" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="AE53" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF53" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="AE54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T55" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="U55" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z55" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD55" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="AE55" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF55" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="U56" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z56" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD56" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="AE56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF56" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD60" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="AE60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q61" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="R61" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="U61" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z61" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD61" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="AE61" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG61" s="3" t="s">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AG36"/>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4730" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4830" uniqueCount="890">
   <si>
     <t>ID PDV</t>
   </si>
@@ -2559,6 +2559,141 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1035227940_DBD_INGRESO_PDV_81723_23_09_2026_11_06_40.jpg</t>
+  </si>
+  <si>
+    <t>7825063</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Punto Pruebas</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>4.4551284</t>
+  </si>
+  <si>
+    <t>-75.2343539</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:25:42</t>
+  </si>
+  <si>
+    <t>0h 30m</t>
+  </si>
+  <si>
+    <t>23/09/2026 13:32:37</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/71/4714_1007634699_DBD_SALIDA_PDV_26399_23_09_2026_13_32_34_910_55438995030919_57318.jpg</t>
+  </si>
+  <si>
+    <t>4.455095</t>
+  </si>
+  <si>
+    <t>-75.23432333333334</t>
+  </si>
+  <si>
+    <t>1h 6m</t>
+  </si>
+  <si>
+    <t>204227</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1007634699_DBD_INGRESO_PDV_65351_23_09_2026_12_25_40.jpg</t>
+  </si>
+  <si>
+    <t>7825082</t>
+  </si>
+  <si>
+    <t>4.7559562</t>
+  </si>
+  <si>
+    <t>-74.0466903</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:45:43</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1007627363_DBD_INGRESO_PDV_73576_23_09_2026_12_45_42.jpg</t>
+  </si>
+  <si>
+    <t>7825096</t>
+  </si>
+  <si>
+    <t>4.7559345</t>
+  </si>
+  <si>
+    <t>-74.0466992</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:54:49</t>
+  </si>
+  <si>
+    <t>0h 55m</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:59:41</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/71/4714_1099216880_DBD_SALIDA_PDV_49219_23_09_2026_12_59_35_141_105257341692965_42184.jpg</t>
+  </si>
+  <si>
+    <t>4.755933333333333</t>
+  </si>
+  <si>
+    <t>-74.04670333333334</t>
+  </si>
+  <si>
+    <t>0h 4m</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1099216880_DBD_INGRESO_PDV_52698_23_09_2026_12_54_47.jpg</t>
+  </si>
+  <si>
+    <t>Kam Derco</t>
+  </si>
+  <si>
+    <t>7825182</t>
+  </si>
+  <si>
+    <t>4.6190571</t>
+  </si>
+  <si>
+    <t>-74.0862484</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:11:32</t>
+  </si>
+  <si>
+    <t>1h 0m</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:34:05</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/71/4714_1099216880_DBD_SALIDA_PDV_69365_23_09_2026_14_33_59_868_110484976139507_8872.jpg</t>
+  </si>
+  <si>
+    <t>4.618945</t>
+  </si>
+  <si>
+    <t>-74.085695</t>
+  </si>
+  <si>
+    <t>0h 22m</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1099216880_DBD_INGRESO_PDV_21481_23_09_2026_14_11_30.jpg</t>
   </si>
 </sst>
 </file>
@@ -13266,7 +13401,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -17899,6 +18034,314 @@
         <v>68</v>
       </c>
     </row>
+    <row r="62" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q63" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="R63" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="U63" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z63" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD63" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="AE63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF63" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q64" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="U64" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="V64" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="W64" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="X64" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="Y64" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="Z64" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="AA64" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="AB64" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="AD64" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="AG64" s="3" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q65" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="R65" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="U65" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="V65" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="W65" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="X65" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="Y65" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="Z65" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="AA65" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="AB65" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="AD65" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="AG65" s="3" t="s">
+        <v>877</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AG36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4830" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4866" uniqueCount="895">
   <si>
     <t>ID PDV</t>
   </si>
@@ -2561,51 +2561,6 @@
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1035227940_DBD_INGRESO_PDV_81723_23_09_2026_11_06_40.jpg</t>
   </si>
   <si>
-    <t>7825063</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Punto Pruebas</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>4.4551284</t>
-  </si>
-  <si>
-    <t>-75.2343539</t>
-  </si>
-  <si>
-    <t>23/09/2026 12:25:42</t>
-  </si>
-  <si>
-    <t>0h 30m</t>
-  </si>
-  <si>
-    <t>23/09/2026 13:32:37</t>
-  </si>
-  <si>
-    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/71/4714_1007634699_DBD_SALIDA_PDV_26399_23_09_2026_13_32_34_910_55438995030919_57318.jpg</t>
-  </si>
-  <si>
-    <t>4.455095</t>
-  </si>
-  <si>
-    <t>-75.23432333333334</t>
-  </si>
-  <si>
-    <t>1h 6m</t>
-  </si>
-  <si>
-    <t>204227</t>
-  </si>
-  <si>
-    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1007634699_DBD_INGRESO_PDV_65351_23_09_2026_12_25_40.jpg</t>
-  </si>
-  <si>
     <t>7825082</t>
   </si>
   <si>
@@ -2694,6 +2649,66 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1099216880_DBD_INGRESO_PDV_21481_23_09_2026_14_11_30.jpg</t>
+  </si>
+  <si>
+    <t>7825311</t>
+  </si>
+  <si>
+    <t>5.34293227</t>
+  </si>
+  <si>
+    <t>-72.38147069</t>
+  </si>
+  <si>
+    <t>24/09/2026 06:03:38</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1073504751_DBD_INGRESO_PDV_82301_24_09_2026_06_03_36.jpg</t>
+  </si>
+  <si>
+    <t>7825328</t>
+  </si>
+  <si>
+    <t>3655</t>
+  </si>
+  <si>
+    <t>Homecenter Ibague</t>
+  </si>
+  <si>
+    <t>IBAGUE</t>
+  </si>
+  <si>
+    <t>4.438648333333333</t>
+  </si>
+  <si>
+    <t>-75.18643833333334</t>
+  </si>
+  <si>
+    <t>24/09/2026 07:39:06</t>
+  </si>
+  <si>
+    <t>4h 0m</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1099216880_DBD_INGRESO_PDV_84685_24_09_2026_07_39_05.jpg</t>
+  </si>
+  <si>
+    <t>7825353</t>
+  </si>
+  <si>
+    <t>2.955918333333333</t>
+  </si>
+  <si>
+    <t>-75.28359166666668</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:00:59</t>
+  </si>
+  <si>
+    <t>6h 30m</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1075284723_DBD_INGRESO_PDV_70923_24_09_2026_08_00_55.jpg</t>
   </si>
 </sst>
 </file>
@@ -2733,9 +2748,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -13401,7 +13417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG65"/>
+  <dimension ref="A1:AG67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -18039,76 +18055,58 @@
         <v>845</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>846</v>
+        <v>304</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>847</v>
+        <v>305</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>847</v>
+        <v>305</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>33</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>252</v>
+        <v>32</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>848</v>
+        <v>123</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>34</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>158</v>
+        <v>308</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>159</v>
+        <v>309</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>40</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>467</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>854</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>855</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>856</v>
+        <v>469</v>
       </c>
       <c r="Z62" s="3" t="s">
-        <v>857</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>538</v>
+        <v>475</v>
       </c>
       <c r="AD62" s="3" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>42</v>
@@ -18119,7 +18117,7 @@
     </row>
     <row r="63" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>860</v>
+        <v>850</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>304</v>
@@ -18146,57 +18144,72 @@
         <v>34</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>308</v>
+        <v>42</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>309</v>
+        <v>43</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
       <c r="S63" s="3" t="s">
         <v>467</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>469</v>
+        <v>854</v>
+      </c>
+      <c r="V63" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="W63" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="X63" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="Y63" s="3" t="s">
+        <v>858</v>
       </c>
       <c r="Z63" s="3" t="s">
-        <v>475</v>
+        <v>859</v>
+      </c>
+      <c r="AA63" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="AB63" s="3" t="s">
+        <v>538</v>
       </c>
       <c r="AD63" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="AE63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF63" s="3" t="s">
-        <v>43</v>
+        <v>861</v>
+      </c>
+      <c r="AG63" s="3" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="64" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>304</v>
+        <v>161</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>305</v>
+        <v>162</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>305</v>
+        <v>162</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>33</v>
@@ -18220,126 +18233,277 @@
         <v>68</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="S64" s="3" t="s">
         <v>467</v>
       </c>
       <c r="T64" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="U64" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="V64" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="U64" s="3" t="s">
+      <c r="W64" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="V64" s="3" t="s">
+      <c r="X64" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="W64" s="3" t="s">
+      <c r="Y64" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="X64" s="3" t="s">
+      <c r="Z64" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="Y64" s="3" t="s">
+      <c r="AA64" s="3" t="s">
         <v>873</v>
-      </c>
-      <c r="Z64" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="AA64" s="3" t="s">
-        <v>875</v>
       </c>
       <c r="AB64" s="3" t="s">
         <v>538</v>
       </c>
       <c r="AD64" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="AG64" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="N65" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q65" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="AG64" s="3" t="s">
+      <c r="R65" s="4" t="s">
         <v>877</v>
       </c>
-    </row>
-    <row r="65" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="S65" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T65" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L65" s="3" t="s">
+      <c r="U65" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA65" s="4"/>
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4"/>
+      <c r="AD65" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="AE65" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF65" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG65" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O66" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q66" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="R66" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="S66" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T66" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="U66" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA66" s="4"/>
+      <c r="AB66" s="4"/>
+      <c r="AC66" s="4"/>
+      <c r="AD66" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="AE66" s="4"/>
+      <c r="AF66" s="4"/>
+      <c r="AG66" s="4" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="M65" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="O65" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P65" s="3" t="s">
+      <c r="M67" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="N67" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="O67" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="P67" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q67" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="R67" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="S67" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T67" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="U67" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA67" s="4"/>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="4"/>
+      <c r="AD67" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="AE67" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF67" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG67" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="Q65" s="3" t="s">
-        <v>879</v>
-      </c>
-      <c r="R65" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="S65" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="T65" s="3" t="s">
-        <v>881</v>
-      </c>
-      <c r="U65" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="V65" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="W65" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="X65" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="Y65" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="Z65" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="AA65" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="AB65" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="AD65" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="AG65" s="3" t="s">
-        <v>877</v>
       </c>
     </row>
   </sheetData>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4866" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4907" uniqueCount="905">
   <si>
     <t>ID PDV</t>
   </si>
@@ -2709,6 +2709,36 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1075284723_DBD_INGRESO_PDV_70923_24_09_2026_08_00_55.jpg</t>
+  </si>
+  <si>
+    <t>7825361</t>
+  </si>
+  <si>
+    <t>4.657185</t>
+  </si>
+  <si>
+    <t>-74.07215833333333</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:07:58</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1000126464_DBD_INGRESO_PDV_76030_24_09_2026_08_07_56.jpg</t>
+  </si>
+  <si>
+    <t>7825370</t>
+  </si>
+  <si>
+    <t>3.472675</t>
+  </si>
+  <si>
+    <t>-76.52840333333333</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:13:48</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/94412336_DBD_INGRESO_PDV_60562_24_09_2026_08_13_47.jpg</t>
   </si>
 </sst>
 </file>
@@ -13417,7 +13447,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG67"/>
+  <dimension ref="A1:AG69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -18506,6 +18536,158 @@
         <v>68</v>
       </c>
     </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N68" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="O68" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q68" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="R68" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="S68" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T68" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="U68" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA68" s="4"/>
+      <c r="AB68" s="4"/>
+      <c r="AC68" s="4"/>
+      <c r="AD68" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="AE68" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF68" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG68" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="N69" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="O69" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q69" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="R69" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="S69" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T69" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="U69" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA69" s="4"/>
+      <c r="AB69" s="4"/>
+      <c r="AC69" s="4"/>
+      <c r="AD69" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="AE69" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF69" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG69" s="4"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AG36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4907" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5055" uniqueCount="939">
   <si>
     <t>ID PDV</t>
   </si>
@@ -2739,13 +2739,115 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/94412336_DBD_INGRESO_PDV_60562_24_09_2026_08_13_47.jpg</t>
+  </si>
+  <si>
+    <t>7825419</t>
+  </si>
+  <si>
+    <t>10.4144383</t>
+  </si>
+  <si>
+    <t>-75.529947</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:42:44</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1043635140_DBD_INGRESO_PDV_83815_24_09_2026_08_42_42.jpg</t>
+  </si>
+  <si>
+    <t>7825440</t>
+  </si>
+  <si>
+    <t>4.80371</t>
+  </si>
+  <si>
+    <t>-75.71789666666668</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:52:59</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1088349837_DBD_INGRESO_PDV_77246_24_09_2026_08_52_57.jpg</t>
+  </si>
+  <si>
+    <t>7825441</t>
+  </si>
+  <si>
+    <t>7.8860797</t>
+  </si>
+  <si>
+    <t>-72.4934146</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:53:43</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1090436828_DBD_INGRESO_PDV_44410_24_09_2026_08_53_42.jpg</t>
+  </si>
+  <si>
+    <t>7825451</t>
+  </si>
+  <si>
+    <t>4.892531666666667</t>
+  </si>
+  <si>
+    <t>-74.03437166666666</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:56:50</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1075688960_DBD_INGRESO_PDV_73702_24_09_2026_08_56_49.jpg</t>
+  </si>
+  <si>
+    <t>7825457</t>
+  </si>
+  <si>
+    <t>4.678278333333334</t>
+  </si>
+  <si>
+    <t>-74.118235</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:59:45</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/80115103_DBD_INGRESO_PDV_88416_24_09_2026_08_59_44.jpg</t>
+  </si>
+  <si>
+    <t>7825459</t>
+  </si>
+  <si>
+    <t>-76.31068333333333</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:00:38</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1113649647_DBD_INGRESO_PDV_85040_24_09_2026_09_00_37.jpg</t>
+  </si>
+  <si>
+    <t>7825461</t>
+  </si>
+  <si>
+    <t>3.36859</t>
+  </si>
+  <si>
+    <t>-76.52755</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:01:14</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1114813506_DBD_INGRESO_PDV_48850_24_09_2026_09_01_12.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -2756,6 +2858,13 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2775,18 +2884,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -13447,7 +13558,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG69"/>
+  <dimension ref="A1:AG76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -18688,6 +18799,547 @@
       </c>
       <c r="AG69" s="4"/>
     </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="M70" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q70" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="R70" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="S70" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T70" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="U70" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA70" s="4"/>
+      <c r="AB70" s="4"/>
+      <c r="AC70" s="4"/>
+      <c r="AD70" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="AE70" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF70" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG70" s="4"/>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q71" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="R71" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="S71" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T71" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="U71" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA71" s="4"/>
+      <c r="AB71" s="4"/>
+      <c r="AC71" s="4"/>
+      <c r="AD71" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="AE71" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF71" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG71" s="4"/>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="O72" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q72" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="R72" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="S72" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T72" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="U72" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA72" s="4"/>
+      <c r="AB72" s="4"/>
+      <c r="AC72" s="4"/>
+      <c r="AD72" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="AE72" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF72" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG72" s="4"/>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q73" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="R73" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="S73" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T73" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="U73" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="V73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA73" s="4"/>
+      <c r="AB73" s="4"/>
+      <c r="AC73" s="4"/>
+      <c r="AD73" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="AE73" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF73" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG73" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M74" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="O74" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q74" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="R74" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="S74" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T74" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="U74" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="V74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA74" s="4"/>
+      <c r="AB74" s="4"/>
+      <c r="AC74" s="4"/>
+      <c r="AD74" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="AE74" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF74" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG74" s="4"/>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="O75" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="P75" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q75" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="R75" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="S75" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T75" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="U75" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA75" s="4"/>
+      <c r="AB75" s="4"/>
+      <c r="AC75" s="4"/>
+      <c r="AD75" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="AE75" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF75" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG75" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q76" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="R76" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="S76" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T76" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="U76" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA76" s="4"/>
+      <c r="AB76" s="4"/>
+      <c r="AC76" s="4"/>
+      <c r="AD76" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="AE76" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF76" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG76" s="4"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AG36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5055" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5337" uniqueCount="1007">
   <si>
     <t>ID PDV</t>
   </si>
@@ -2841,6 +2841,210 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1114813506_DBD_INGRESO_PDV_48850_24_09_2026_09_01_12.jpg</t>
+  </si>
+  <si>
+    <t>7825475</t>
+  </si>
+  <si>
+    <t>11.2279805</t>
+  </si>
+  <si>
+    <t>-74.1726656</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:07:30</t>
+  </si>
+  <si>
+    <t>2h 0m</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1110533250_DBD_INGRESO_PDV_5148_24_09_2026_09_07_29.jpg</t>
+  </si>
+  <si>
+    <t>7825486</t>
+  </si>
+  <si>
+    <t>4.5888583333333335</t>
+  </si>
+  <si>
+    <t>-74.20559166666666</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:13:39</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1014305216_DBD_INGRESO_PDV_78302_24_09_2026_09_13_38.jpg</t>
+  </si>
+  <si>
+    <t>7825490</t>
+  </si>
+  <si>
+    <t>7.1154507</t>
+  </si>
+  <si>
+    <t>-73.1203353</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:14:28</t>
+  </si>
+  <si>
+    <t>5h 30m</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1102716954_DBD_INGRESO_PDV_4965_24_09_2026_09_14_27.jpg</t>
+  </si>
+  <si>
+    <t>7825491</t>
+  </si>
+  <si>
+    <t>8.777685</t>
+  </si>
+  <si>
+    <t>-75.862705</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:15:27</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1067881033_DBD_INGRESO_PDV_74568_24_09_2026_09_15_26.jpg</t>
+  </si>
+  <si>
+    <t>7825498</t>
+  </si>
+  <si>
+    <t>4.6851055</t>
+  </si>
+  <si>
+    <t>-74.0787076</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:20:30</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1028865500_DBD_INGRESO_PDV_9834_24_09_2026_09_20_30.jpg</t>
+  </si>
+  <si>
+    <t>7825499</t>
+  </si>
+  <si>
+    <t>10.9474921</t>
+  </si>
+  <si>
+    <t>-74.7834235</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:20:37</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/72098375_DBD_INGRESO_PDV_62257_24_09_2026_09_20_36.jpg</t>
+  </si>
+  <si>
+    <t>7825501</t>
+  </si>
+  <si>
+    <t>6.2338216</t>
+  </si>
+  <si>
+    <t>-75.6049405</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:22:00</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/71780913_DBD_INGRESO_PDV_23588_24_09_2026_09_21_58.jpg</t>
+  </si>
+  <si>
+    <t>7825553</t>
+  </si>
+  <si>
+    <t>10.49359</t>
+  </si>
+  <si>
+    <t>-73.26722166666667</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:51:06</t>
+  </si>
+  <si>
+    <t>6h 50m</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1065626573_DBD_INGRESO_PDV_10578_24_09_2026_09_51_03.jpg</t>
+  </si>
+  <si>
+    <t>7825559</t>
+  </si>
+  <si>
+    <t>11.015165000000001</t>
+  </si>
+  <si>
+    <t>-74.82931333333333</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:55:28</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/72257237_DBD_INGRESO_PDV_23780_24_09_2026_09_55_26.jpg</t>
+  </si>
+  <si>
+    <t>7825566</t>
+  </si>
+  <si>
+    <t>4.7007904</t>
+  </si>
+  <si>
+    <t>-74.2308192</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:59:54</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1070464010_DBD_INGRESO_PDV_14619_24_09_2026_09_59_53.jpg</t>
+  </si>
+  <si>
+    <t>7825567</t>
+  </si>
+  <si>
+    <t>6.212864999999999</t>
+  </si>
+  <si>
+    <t>-75.57785833333334</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:59:57</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1039448347_DBD_INGRESO_PDV_29338_24_09_2026_09_59_38.jpg</t>
+  </si>
+  <si>
+    <t>7825576</t>
+  </si>
+  <si>
+    <t>4.618455</t>
+  </si>
+  <si>
+    <t>-74.08615</t>
+  </si>
+  <si>
+    <t>24/09/2026 10:03:50</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1233490257_DBD_INGRESO_PDV_2954_24_09_2026_10_03_48.jpg</t>
+  </si>
+  <si>
+    <t>7825581</t>
+  </si>
+  <si>
+    <t>4.6191872</t>
+  </si>
+  <si>
+    <t>-74.0864082</t>
+  </si>
+  <si>
+    <t>24/09/2026 10:04:54</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1001277768_DBD_INGRESO_PDV_8962_24_09_2026_10_04_53.jpg</t>
   </si>
 </sst>
 </file>
@@ -2893,7 +3097,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13558,7 +13762,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG76"/>
+  <dimension ref="A1:AG89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -18416,7 +18620,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>875</v>
       </c>
@@ -18438,10 +18642,6 @@
       <c r="G65" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
       <c r="L65" s="4" t="s">
         <v>123</v>
       </c>
@@ -18472,16 +18672,9 @@
       <c r="U65" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
       <c r="Z65" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA65" s="4"/>
-      <c r="AB65" s="4"/>
-      <c r="AC65" s="4"/>
       <c r="AD65" s="4" t="s">
         <v>879</v>
       </c>
@@ -18495,7 +18688,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>880</v>
       </c>
@@ -18517,11 +18710,6 @@
       <c r="G66" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
       <c r="M66" s="4" t="s">
         <v>883</v>
       </c>
@@ -18549,26 +18737,17 @@
       <c r="U66" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
       <c r="Z66" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA66" s="4"/>
-      <c r="AB66" s="4"/>
-      <c r="AC66" s="4"/>
       <c r="AD66" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="AE66" s="4"/>
-      <c r="AF66" s="4"/>
       <c r="AG66" s="4" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>889</v>
       </c>
@@ -18590,10 +18769,6 @@
       <c r="G67" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
       <c r="L67" s="4" t="s">
         <v>123</v>
       </c>
@@ -18624,16 +18799,9 @@
       <c r="U67" s="4" t="s">
         <v>893</v>
       </c>
-      <c r="V67" s="4"/>
-      <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
-      <c r="Y67" s="4"/>
       <c r="Z67" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA67" s="4"/>
-      <c r="AB67" s="4"/>
-      <c r="AC67" s="4"/>
       <c r="AD67" s="4" t="s">
         <v>894</v>
       </c>
@@ -18647,14 +18815,13 @@
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>895</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C68" s="4"/>
       <c r="D68" s="4" t="s">
         <v>208</v>
       </c>
@@ -18667,11 +18834,6 @@
       <c r="G68" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
       <c r="M68" s="4" t="s">
         <v>34</v>
       </c>
@@ -18699,16 +18861,9 @@
       <c r="U68" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
-      <c r="X68" s="4"/>
-      <c r="Y68" s="4"/>
       <c r="Z68" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA68" s="4"/>
-      <c r="AB68" s="4"/>
-      <c r="AC68" s="4"/>
       <c r="AD68" s="4" t="s">
         <v>899</v>
       </c>
@@ -18722,7 +18877,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>900</v>
       </c>
@@ -18744,10 +18899,6 @@
       <c r="G69" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
       <c r="L69" s="4" t="s">
         <v>123</v>
       </c>
@@ -18778,16 +18929,9 @@
       <c r="U69" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
-      <c r="X69" s="4"/>
-      <c r="Y69" s="4"/>
       <c r="Z69" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA69" s="4"/>
-      <c r="AB69" s="4"/>
-      <c r="AC69" s="4"/>
       <c r="AD69" s="4" t="s">
         <v>904</v>
       </c>
@@ -18797,9 +18941,8 @@
       <c r="AF69" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AG69" s="4"/>
-    </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>905</v>
       </c>
@@ -18821,10 +18964,6 @@
       <c r="G70" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
       <c r="L70" s="4" t="s">
         <v>470</v>
       </c>
@@ -18855,16 +18994,9 @@
       <c r="U70" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="V70" s="4"/>
-      <c r="W70" s="4"/>
-      <c r="X70" s="4"/>
-      <c r="Y70" s="4"/>
       <c r="Z70" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA70" s="4"/>
-      <c r="AB70" s="4"/>
-      <c r="AC70" s="4"/>
       <c r="AD70" s="4" t="s">
         <v>909</v>
       </c>
@@ -18874,9 +19006,8 @@
       <c r="AF70" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AG70" s="4"/>
-    </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>910</v>
       </c>
@@ -18898,10 +19029,6 @@
       <c r="G71" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
       <c r="L71" s="4" t="s">
         <v>123</v>
       </c>
@@ -18932,16 +19059,9 @@
       <c r="U71" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="V71" s="4"/>
-      <c r="W71" s="4"/>
-      <c r="X71" s="4"/>
-      <c r="Y71" s="4"/>
       <c r="Z71" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA71" s="4"/>
-      <c r="AB71" s="4"/>
-      <c r="AC71" s="4"/>
       <c r="AD71" s="4" t="s">
         <v>914</v>
       </c>
@@ -18951,9 +19071,8 @@
       <c r="AF71" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AG71" s="4"/>
-    </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>915</v>
       </c>
@@ -18975,10 +19094,6 @@
       <c r="G72" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
       <c r="L72" s="4" t="s">
         <v>123</v>
       </c>
@@ -19009,16 +19124,9 @@
       <c r="U72" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="V72" s="4"/>
-      <c r="W72" s="4"/>
-      <c r="X72" s="4"/>
-      <c r="Y72" s="4"/>
       <c r="Z72" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA72" s="4"/>
-      <c r="AB72" s="4"/>
-      <c r="AC72" s="4"/>
       <c r="AD72" s="4" t="s">
         <v>919</v>
       </c>
@@ -19028,9 +19136,8 @@
       <c r="AF72" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AG72" s="4"/>
-    </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>920</v>
       </c>
@@ -19052,10 +19159,6 @@
       <c r="G73" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
       <c r="L73" s="4" t="s">
         <v>123</v>
       </c>
@@ -19086,16 +19189,9 @@
       <c r="U73" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="V73" s="4"/>
-      <c r="W73" s="4"/>
-      <c r="X73" s="4"/>
-      <c r="Y73" s="4"/>
       <c r="Z73" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA73" s="4"/>
-      <c r="AB73" s="4"/>
-      <c r="AC73" s="4"/>
       <c r="AD73" s="4" t="s">
         <v>924</v>
       </c>
@@ -19109,7 +19205,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>925</v>
       </c>
@@ -19131,10 +19227,6 @@
       <c r="G74" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
       <c r="L74" s="4" t="s">
         <v>123</v>
       </c>
@@ -19165,16 +19257,9 @@
       <c r="U74" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="V74" s="4"/>
-      <c r="W74" s="4"/>
-      <c r="X74" s="4"/>
-      <c r="Y74" s="4"/>
       <c r="Z74" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA74" s="4"/>
-      <c r="AB74" s="4"/>
-      <c r="AC74" s="4"/>
       <c r="AD74" s="4" t="s">
         <v>929</v>
       </c>
@@ -19184,9 +19269,8 @@
       <c r="AF74" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AG74" s="4"/>
-    </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>930</v>
       </c>
@@ -19208,10 +19292,6 @@
       <c r="G75" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
       <c r="L75" s="4" t="s">
         <v>123</v>
       </c>
@@ -19242,16 +19322,9 @@
       <c r="U75" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="V75" s="4"/>
-      <c r="W75" s="4"/>
-      <c r="X75" s="4"/>
-      <c r="Y75" s="4"/>
       <c r="Z75" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA75" s="4"/>
-      <c r="AB75" s="4"/>
-      <c r="AC75" s="4"/>
       <c r="AD75" s="4" t="s">
         <v>933</v>
       </c>
@@ -19265,7 +19338,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>934</v>
       </c>
@@ -19287,11 +19360,6 @@
       <c r="G76" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
       <c r="M76" s="4" t="s">
         <v>177</v>
       </c>
@@ -19319,16 +19387,9 @@
       <c r="U76" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
-      <c r="X76" s="4"/>
-      <c r="Y76" s="4"/>
       <c r="Z76" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AA76" s="4"/>
-      <c r="AB76" s="4"/>
-      <c r="AC76" s="4"/>
       <c r="AD76" s="4" t="s">
         <v>938</v>
       </c>
@@ -19338,7 +19399,878 @@
       <c r="AF76" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AG76" s="4"/>
+    </row>
+    <row r="77" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q77" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="R77" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="S77" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T77" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="U77" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="Z77" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD77" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="AE77" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF77" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG77" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q78" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="R78" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="S78" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T78" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="U78" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z78" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD78" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="AE78" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF78" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG78" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="O79" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q79" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="R79" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="S79" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T79" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="U79" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="Z79" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD79" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="AE79" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF79" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG79" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M80" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="O80" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q80" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="R80" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="S80" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T80" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="U80" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z80" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD80" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="AE80" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF80" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG80" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N81" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q81" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="R81" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="S81" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T81" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="U81" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z81" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD81" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="AE81" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF81" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="82" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M82" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="N82" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="O82" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="P82" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q82" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="R82" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="S82" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T82" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="U82" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z82" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD82" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="AE82" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF82" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG82" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="83" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N83" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O83" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="P83" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q83" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="R83" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="S83" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T83" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="U83" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z83" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD83" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="AE83" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF83" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG83" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="84" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="N84" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="O84" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="P84" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q84" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="R84" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="S84" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T84" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="U84" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="Z84" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD84" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="AE84" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF84" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="N85" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="O85" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="P85" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q85" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="R85" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="S85" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T85" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="U85" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z85" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD85" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="AE85" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF85" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG85" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N86" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O86" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P86" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q86" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="R86" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="S86" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T86" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="U86" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z86" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD86" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="AE86" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF86" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N87" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="O87" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="P87" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q87" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="R87" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="S87" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T87" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="U87" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z87" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD87" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="AE87" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF87" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG87" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="88" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M88" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N88" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="O88" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="P88" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q88" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="R88" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="S88" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T88" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="U88" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z88" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD88" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AE88" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF88" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG88" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="89" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N89" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="O89" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="P89" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q89" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="R89" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="S89" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T89" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="U89" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z89" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD89" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="AE89" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF89" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AG36"/>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -17,14 +17,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ingresos!$A$1:$AG$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">programacion!$A$1:$AC$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">programacion!$A$1:$AC$149</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5337" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5455" uniqueCount="1043">
   <si>
     <t>ID PDV</t>
   </si>
@@ -1127,21 +1127,6 @@
     <t>10626297</t>
   </si>
   <si>
-    <t>254</t>
-  </si>
-  <si>
-    <t>Exito Laureles.</t>
-  </si>
-  <si>
-    <t>Carrera 81 # 37-100, Medellin</t>
-  </si>
-  <si>
-    <t>10626411</t>
-  </si>
-  <si>
-    <t>01:00:00</t>
-  </si>
-  <si>
     <t>10636531</t>
   </si>
   <si>
@@ -1295,9 +1280,6 @@
     <t>2422</t>
   </si>
   <si>
-    <t>Homecenter Suba</t>
-  </si>
-  <si>
     <t>Carrera 104 # 150C-55, Bogota</t>
   </si>
   <si>
@@ -3045,6 +3027,132 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1001277768_DBD_INGRESO_PDV_8962_24_09_2026_10_04_53.jpg</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:55:07</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/71/4714_1099216880_DBD_SALIDA_PDV_75496_24_09_2026_12_55_06_465_37210903542910_18406.jpg</t>
+  </si>
+  <si>
+    <t>4.439850000000001</t>
+  </si>
+  <si>
+    <t>-75.18529833333334</t>
+  </si>
+  <si>
+    <t>5h 16m</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>24/09/2026 10:16:06</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/71/4714_1110533250_DBD_SALIDA_PDV_61889_24_09_2026_10_16_04_401_151871082557820_19709.jpg</t>
+  </si>
+  <si>
+    <t>11.22553</t>
+  </si>
+  <si>
+    <t>-74.17383</t>
+  </si>
+  <si>
+    <t>1h 8m</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>7825597</t>
+  </si>
+  <si>
+    <t>10.383116666666666</t>
+  </si>
+  <si>
+    <t>-75.46904333333333</t>
+  </si>
+  <si>
+    <t>24/09/2026 10:16:13</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1002247264_DBD_INGRESO_PDV_9261_24_09_2026_10_16_11.jpg</t>
+  </si>
+  <si>
+    <t>7825599</t>
+  </si>
+  <si>
+    <t>11.225593333333332</t>
+  </si>
+  <si>
+    <t>-74.17383333333333</t>
+  </si>
+  <si>
+    <t>24/09/2026 10:16:19</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1110533250_DBD_INGRESO_PDV_1666_24_09_2026_10_16_17.jpg</t>
+  </si>
+  <si>
+    <t>7825600</t>
+  </si>
+  <si>
+    <t>4.7302454</t>
+  </si>
+  <si>
+    <t>-74.0330946</t>
+  </si>
+  <si>
+    <t>24/09/2026 10:16:31</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/11225449_DBD_INGRESO_PDV_29028_24_09_2026_10_16_30.jpg</t>
+  </si>
+  <si>
+    <t>7825697</t>
+  </si>
+  <si>
+    <t>4.7559535</t>
+  </si>
+  <si>
+    <t>-74.046699</t>
+  </si>
+  <si>
+    <t>24/09/2026 11:11:10</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1007627363_DBD_INGRESO_PDV_20288_24_09_2026_11_11_08.jpg</t>
+  </si>
+  <si>
+    <t>7825705</t>
+  </si>
+  <si>
+    <t>6.2528500000000005</t>
+  </si>
+  <si>
+    <t>-75.582745</t>
+  </si>
+  <si>
+    <t>24/09/2026 11:16:03</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1035227940_DBD_INGRESO_PDV_84348_24_09_2026_11_16_02.jpg</t>
+  </si>
+  <si>
+    <t>7825764</t>
+  </si>
+  <si>
+    <t>6.24944726</t>
+  </si>
+  <si>
+    <t>-75.58461479</t>
+  </si>
+  <si>
+    <t>24/09/2026 11:44:10</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1007634699_DBD_INGRESO_PDV_62087_24_09_2026_11_44_08.jpg</t>
   </si>
 </sst>
 </file>
@@ -3433,8 +3541,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC150"/>
+  <dimension ref="A1:AC149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -3853,7 +3964,7 @@
         <v>68</v>
       </c>
       <c r="V6" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="W6" t="s">
         <v>86</v>
@@ -3918,7 +4029,7 @@
         <v>43</v>
       </c>
       <c r="V7" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="W7" t="s">
         <v>86</v>
@@ -3989,7 +4100,7 @@
         <v>68</v>
       </c>
       <c r="V8" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="W8" t="s">
         <v>86</v>
@@ -4261,7 +4372,7 @@
         <v>68</v>
       </c>
       <c r="V12" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="W12" t="s">
         <v>86</v>
@@ -4332,7 +4443,7 @@
         <v>68</v>
       </c>
       <c r="V13" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="W13" t="s">
         <v>86</v>
@@ -4403,7 +4514,7 @@
         <v>68</v>
       </c>
       <c r="V14" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="W14" t="s">
         <v>86</v>
@@ -4471,7 +4582,7 @@
         <v>68</v>
       </c>
       <c r="V15" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="W15" t="s">
         <v>45</v>
@@ -5145,7 +5256,7 @@
         <v>68</v>
       </c>
       <c r="V25" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="W25" t="s">
         <v>45</v>
@@ -5216,7 +5327,7 @@
         <v>68</v>
       </c>
       <c r="V26" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="W26" t="s">
         <v>45</v>
@@ -5287,7 +5398,7 @@
         <v>68</v>
       </c>
       <c r="V27" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="W27" t="s">
         <v>86</v>
@@ -5358,7 +5469,7 @@
         <v>68</v>
       </c>
       <c r="V28" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="W28" t="s">
         <v>45</v>
@@ -5429,7 +5540,7 @@
         <v>68</v>
       </c>
       <c r="V29" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="W29" t="s">
         <v>45</v>
@@ -5500,7 +5611,7 @@
         <v>68</v>
       </c>
       <c r="V30" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="W30" t="s">
         <v>45</v>
@@ -5843,7 +5954,7 @@
         <v>68</v>
       </c>
       <c r="V35" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="W35" t="s">
         <v>45</v>
@@ -5908,7 +6019,7 @@
         <v>43</v>
       </c>
       <c r="V36" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="W36" t="s">
         <v>45</v>
@@ -6514,7 +6625,7 @@
         <v>43</v>
       </c>
       <c r="V45" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W45" t="s">
         <v>45</v>
@@ -6585,7 +6696,7 @@
         <v>68</v>
       </c>
       <c r="V46" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="W46" t="s">
         <v>45</v>
@@ -6656,7 +6767,7 @@
         <v>68</v>
       </c>
       <c r="V47" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="W47" t="s">
         <v>45</v>
@@ -6727,7 +6838,7 @@
         <v>68</v>
       </c>
       <c r="V48" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="W48" t="s">
         <v>45</v>
@@ -6798,7 +6909,7 @@
         <v>68</v>
       </c>
       <c r="V49" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="W49" t="s">
         <v>45</v>
@@ -6869,7 +6980,7 @@
         <v>68</v>
       </c>
       <c r="V50" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="W50" t="s">
         <v>45</v>
@@ -6940,7 +7051,7 @@
         <v>68</v>
       </c>
       <c r="V51" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="W51" t="s">
         <v>45</v>
@@ -7011,7 +7122,7 @@
         <v>68</v>
       </c>
       <c r="V52" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="W52" t="s">
         <v>45</v>
@@ -7413,7 +7524,7 @@
         <v>68</v>
       </c>
       <c r="V58" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="W58" t="s">
         <v>45</v>
@@ -7484,7 +7595,7 @@
         <v>68</v>
       </c>
       <c r="V59" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="W59" t="s">
         <v>45</v>
@@ -7549,7 +7660,7 @@
         <v>43</v>
       </c>
       <c r="V60" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="W60" t="s">
         <v>45</v>
@@ -7620,7 +7731,7 @@
         <v>68</v>
       </c>
       <c r="V61" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="W61" t="s">
         <v>45</v>
@@ -8451,7 +8562,7 @@
         <v>43</v>
       </c>
       <c r="V73" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="W73" t="s">
         <v>45</v>
@@ -8522,7 +8633,7 @@
         <v>68</v>
       </c>
       <c r="V74" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="W74" t="s">
         <v>45</v>
@@ -8587,7 +8698,7 @@
         <v>43</v>
       </c>
       <c r="V75" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="W75" t="s">
         <v>45</v>
@@ -8658,7 +8769,7 @@
         <v>68</v>
       </c>
       <c r="V76" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="W76" t="s">
         <v>45</v>
@@ -8723,7 +8834,7 @@
         <v>43</v>
       </c>
       <c r="V77" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="W77" t="s">
         <v>45</v>
@@ -8743,13 +8854,13 @@
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B78" t="s">
-        <v>423</v>
+        <v>231</v>
       </c>
       <c r="C78" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D78" t="s">
         <v>32</v>
@@ -8794,7 +8905,7 @@
         <v>68</v>
       </c>
       <c r="V78" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="W78" t="s">
         <v>45</v>
@@ -9202,7 +9313,7 @@
         <v>68</v>
       </c>
       <c r="V84" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="W84" t="s">
         <v>45</v>
@@ -9267,7 +9378,7 @@
         <v>43</v>
       </c>
       <c r="V85" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="W85" t="s">
         <v>45</v>
@@ -9276,7 +9387,7 @@
         <v>58</v>
       </c>
       <c r="Y85" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="Z85" t="s">
         <v>48</v>
@@ -9358,34 +9469,34 @@
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>367</v>
+        <v>131</v>
       </c>
       <c r="B87" t="s">
-        <v>368</v>
+        <v>132</v>
       </c>
       <c r="C87" t="s">
-        <v>369</v>
+        <v>133</v>
       </c>
       <c r="D87" t="s">
-        <v>252</v>
+        <v>32</v>
       </c>
       <c r="I87" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J87" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="K87" t="s">
         <v>35</v>
       </c>
       <c r="L87" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="M87" t="s">
-        <v>202</v>
+        <v>136</v>
       </c>
       <c r="N87" t="s">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="O87" t="s">
         <v>39</v>
@@ -9402,14 +9513,8 @@
       <c r="S87" t="s">
         <v>43</v>
       </c>
-      <c r="T87" t="s">
-        <v>67</v>
-      </c>
-      <c r="U87" t="s">
-        <v>68</v>
-      </c>
       <c r="V87" t="s">
-        <v>370</v>
+        <v>420</v>
       </c>
       <c r="W87" t="s">
         <v>45</v>
@@ -9418,45 +9523,45 @@
         <v>58</v>
       </c>
       <c r="Y87" t="s">
-        <v>75</v>
+        <v>421</v>
       </c>
       <c r="Z87" t="s">
-        <v>254</v>
+        <v>60</v>
       </c>
       <c r="AA87" t="s">
-        <v>371</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>131</v>
+        <v>344</v>
       </c>
       <c r="B88" t="s">
-        <v>132</v>
+        <v>345</v>
       </c>
       <c r="C88" t="s">
-        <v>133</v>
+        <v>346</v>
       </c>
       <c r="D88" t="s">
         <v>32</v>
       </c>
       <c r="I88" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="J88" t="s">
-        <v>134</v>
+        <v>347</v>
       </c>
       <c r="K88" t="s">
         <v>35</v>
       </c>
       <c r="L88" t="s">
-        <v>135</v>
+        <v>348</v>
       </c>
       <c r="M88" t="s">
-        <v>136</v>
+        <v>349</v>
       </c>
       <c r="N88" t="s">
-        <v>137</v>
+        <v>350</v>
       </c>
       <c r="O88" t="s">
         <v>39</v>
@@ -9473,8 +9578,14 @@
       <c r="S88" t="s">
         <v>43</v>
       </c>
+      <c r="T88" t="s">
+        <v>67</v>
+      </c>
+      <c r="U88" t="s">
+        <v>68</v>
+      </c>
       <c r="V88" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="W88" t="s">
         <v>45</v>
@@ -9483,45 +9594,45 @@
         <v>58</v>
       </c>
       <c r="Y88" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="Z88" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA88" t="s">
-        <v>206</v>
+        <v>376</v>
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>344</v>
+        <v>198</v>
       </c>
       <c r="B89" t="s">
-        <v>345</v>
+        <v>199</v>
       </c>
       <c r="C89" t="s">
-        <v>346</v>
+        <v>200</v>
       </c>
       <c r="D89" t="s">
         <v>32</v>
       </c>
       <c r="I89" t="s">
-        <v>222</v>
+        <v>80</v>
       </c>
       <c r="J89" t="s">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="K89" t="s">
         <v>35</v>
       </c>
       <c r="L89" t="s">
-        <v>348</v>
+        <v>201</v>
       </c>
       <c r="M89" t="s">
-        <v>349</v>
+        <v>202</v>
       </c>
       <c r="N89" t="s">
-        <v>350</v>
+        <v>203</v>
       </c>
       <c r="O89" t="s">
         <v>39</v>
@@ -9545,7 +9656,7 @@
         <v>68</v>
       </c>
       <c r="V89" t="s">
-        <v>438</v>
+        <v>204</v>
       </c>
       <c r="W89" t="s">
         <v>45</v>
@@ -9554,45 +9665,45 @@
         <v>58</v>
       </c>
       <c r="Y89" t="s">
-        <v>439</v>
+        <v>205</v>
       </c>
       <c r="Z89" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="AA89" t="s">
-        <v>381</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="B90" t="s">
-        <v>199</v>
+        <v>123</v>
       </c>
       <c r="C90" t="s">
-        <v>200</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
         <v>32</v>
       </c>
       <c r="I90" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J90" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="K90" t="s">
         <v>35</v>
       </c>
       <c r="L90" t="s">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="M90" t="s">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="N90" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="O90" t="s">
         <v>39</v>
@@ -9616,7 +9727,7 @@
         <v>68</v>
       </c>
       <c r="V90" t="s">
-        <v>204</v>
+        <v>375</v>
       </c>
       <c r="W90" t="s">
         <v>45</v>
@@ -9625,45 +9736,42 @@
         <v>58</v>
       </c>
       <c r="Y90" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="Z90" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="AA90" t="s">
-        <v>206</v>
+        <v>376</v>
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="B91" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="C91" t="s">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="D91" t="s">
         <v>32</v>
       </c>
       <c r="I91" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J91" t="s">
-        <v>125</v>
-      </c>
-      <c r="K91" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L91" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="M91" t="s">
-        <v>127</v>
+        <v>211</v>
       </c>
       <c r="N91" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
       <c r="O91" t="s">
         <v>39</v>
@@ -9687,51 +9795,54 @@
         <v>68</v>
       </c>
       <c r="V91" t="s">
-        <v>380</v>
+        <v>343</v>
       </c>
       <c r="W91" t="s">
         <v>45</v>
       </c>
       <c r="X91" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="Y91" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Z91" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA91" t="s">
-        <v>381</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>207</v>
+        <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="C92" t="s">
-        <v>209</v>
+        <v>99</v>
       </c>
       <c r="D92" t="s">
         <v>32</v>
       </c>
       <c r="I92" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="J92" t="s">
-        <v>34</v>
+        <v>101</v>
+      </c>
+      <c r="K92" t="s">
+        <v>35</v>
       </c>
       <c r="L92" t="s">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="M92" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="N92" t="s">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="O92" t="s">
         <v>39</v>
@@ -9755,7 +9866,7 @@
         <v>68</v>
       </c>
       <c r="V92" t="s">
-        <v>343</v>
+        <v>105</v>
       </c>
       <c r="W92" t="s">
         <v>45</v>
@@ -9764,45 +9875,45 @@
         <v>70</v>
       </c>
       <c r="Y92" t="s">
-        <v>214</v>
+        <v>47</v>
       </c>
       <c r="Z92" t="s">
         <v>48</v>
       </c>
       <c r="AA92" t="s">
-        <v>215</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="C93" t="s">
-        <v>99</v>
+        <v>192</v>
       </c>
       <c r="D93" t="s">
         <v>32</v>
       </c>
       <c r="I93" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J93" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="K93" t="s">
         <v>35</v>
       </c>
       <c r="L93" t="s">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="M93" t="s">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="N93" t="s">
-        <v>104</v>
+        <v>195</v>
       </c>
       <c r="O93" t="s">
         <v>39</v>
@@ -9819,14 +9930,8 @@
       <c r="S93" t="s">
         <v>43</v>
       </c>
-      <c r="T93" t="s">
-        <v>67</v>
-      </c>
-      <c r="U93" t="s">
-        <v>68</v>
-      </c>
       <c r="V93" t="s">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="W93" t="s">
         <v>45</v>
@@ -9846,34 +9951,34 @@
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="B94" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C94" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="D94" t="s">
         <v>32</v>
       </c>
       <c r="I94" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="J94" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="K94" t="s">
         <v>35</v>
       </c>
       <c r="L94" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="M94" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="N94" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="O94" t="s">
         <v>39</v>
@@ -9891,7 +9996,7 @@
         <v>43</v>
       </c>
       <c r="V94" t="s">
-        <v>196</v>
+        <v>242</v>
       </c>
       <c r="W94" t="s">
         <v>45</v>
@@ -9911,34 +10016,34 @@
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="B95" t="s">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="C95" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="D95" t="s">
         <v>32</v>
       </c>
       <c r="I95" t="s">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="J95" t="s">
-        <v>152</v>
+        <v>223</v>
       </c>
       <c r="K95" t="s">
         <v>35</v>
       </c>
       <c r="L95" t="s">
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="M95" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="N95" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="O95" t="s">
         <v>39</v>
@@ -9956,7 +10061,7 @@
         <v>43</v>
       </c>
       <c r="V95" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="W95" t="s">
         <v>45</v>
@@ -9976,34 +10081,34 @@
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>219</v>
+        <v>285</v>
       </c>
       <c r="B96" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="C96" t="s">
-        <v>221</v>
+        <v>287</v>
       </c>
       <c r="D96" t="s">
         <v>32</v>
       </c>
       <c r="I96" t="s">
-        <v>222</v>
+        <v>100</v>
       </c>
       <c r="J96" t="s">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="K96" t="s">
         <v>35</v>
       </c>
       <c r="L96" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="M96" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="N96" t="s">
-        <v>226</v>
+        <v>290</v>
       </c>
       <c r="O96" t="s">
         <v>39</v>
@@ -10021,7 +10126,7 @@
         <v>43</v>
       </c>
       <c r="V96" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="W96" t="s">
         <v>45</v>
@@ -10041,34 +10146,34 @@
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B97" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C97" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="D97" t="s">
         <v>32</v>
       </c>
       <c r="I97" t="s">
-        <v>100</v>
+        <v>277</v>
       </c>
       <c r="J97" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="K97" t="s">
         <v>35</v>
       </c>
       <c r="L97" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="M97" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="N97" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="O97" t="s">
         <v>39</v>
@@ -10085,8 +10190,14 @@
       <c r="S97" t="s">
         <v>43</v>
       </c>
+      <c r="T97" t="s">
+        <v>67</v>
+      </c>
+      <c r="U97" t="s">
+        <v>68</v>
+      </c>
       <c r="V97" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="W97" t="s">
         <v>45</v>
@@ -10106,34 +10217,34 @@
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="B98" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C98" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D98" t="s">
         <v>32</v>
       </c>
       <c r="I98" t="s">
-        <v>277</v>
+        <v>33</v>
       </c>
       <c r="J98" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="K98" t="s">
         <v>35</v>
       </c>
       <c r="L98" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="M98" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="N98" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="O98" t="s">
         <v>39</v>
@@ -10157,7 +10268,7 @@
         <v>68</v>
       </c>
       <c r="V98" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="W98" t="s">
         <v>45</v>
@@ -10177,34 +10288,34 @@
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>295</v>
+        <v>90</v>
       </c>
       <c r="B99" t="s">
-        <v>296</v>
+        <v>91</v>
       </c>
       <c r="C99" t="s">
-        <v>297</v>
+        <v>92</v>
       </c>
       <c r="D99" t="s">
         <v>32</v>
       </c>
       <c r="I99" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="J99" t="s">
-        <v>298</v>
+        <v>81</v>
       </c>
       <c r="K99" t="s">
         <v>35</v>
       </c>
       <c r="L99" t="s">
-        <v>299</v>
+        <v>93</v>
       </c>
       <c r="M99" t="s">
-        <v>300</v>
+        <v>94</v>
       </c>
       <c r="N99" t="s">
-        <v>301</v>
+        <v>95</v>
       </c>
       <c r="O99" t="s">
         <v>39</v>
@@ -10228,7 +10339,7 @@
         <v>68</v>
       </c>
       <c r="V99" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="W99" t="s">
         <v>45</v>
@@ -10248,34 +10359,34 @@
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B100" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C100" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D100" t="s">
         <v>32</v>
       </c>
       <c r="I100" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J100" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="K100" t="s">
         <v>35</v>
       </c>
       <c r="L100" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="M100" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="N100" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="O100" t="s">
         <v>39</v>
@@ -10299,7 +10410,7 @@
         <v>68</v>
       </c>
       <c r="V100" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="W100" t="s">
         <v>45</v>
@@ -10319,34 +10430,34 @@
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="B101" t="s">
-        <v>107</v>
+        <v>231</v>
       </c>
       <c r="C101" t="s">
-        <v>108</v>
+        <v>232</v>
       </c>
       <c r="D101" t="s">
         <v>32</v>
       </c>
       <c r="I101" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J101" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="K101" t="s">
         <v>35</v>
       </c>
       <c r="L101" t="s">
-        <v>110</v>
+        <v>233</v>
       </c>
       <c r="M101" t="s">
-        <v>111</v>
+        <v>234</v>
       </c>
       <c r="N101" t="s">
-        <v>112</v>
+        <v>235</v>
       </c>
       <c r="O101" t="s">
         <v>39</v>
@@ -10370,7 +10481,7 @@
         <v>68</v>
       </c>
       <c r="V101" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="W101" t="s">
         <v>45</v>
@@ -10390,34 +10501,34 @@
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>230</v>
+        <v>344</v>
       </c>
       <c r="B102" t="s">
-        <v>231</v>
+        <v>345</v>
       </c>
       <c r="C102" t="s">
-        <v>232</v>
+        <v>346</v>
       </c>
       <c r="D102" t="s">
         <v>32</v>
       </c>
       <c r="I102" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="J102" t="s">
-        <v>34</v>
+        <v>347</v>
       </c>
       <c r="K102" t="s">
         <v>35</v>
       </c>
       <c r="L102" t="s">
-        <v>233</v>
+        <v>348</v>
       </c>
       <c r="M102" t="s">
-        <v>234</v>
+        <v>349</v>
       </c>
       <c r="N102" t="s">
-        <v>235</v>
+        <v>350</v>
       </c>
       <c r="O102" t="s">
         <v>39</v>
@@ -10441,7 +10552,7 @@
         <v>68</v>
       </c>
       <c r="V102" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="W102" t="s">
         <v>45</v>
@@ -10461,34 +10572,34 @@
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>344</v>
+        <v>173</v>
       </c>
       <c r="B103" t="s">
-        <v>345</v>
+        <v>174</v>
       </c>
       <c r="C103" t="s">
-        <v>346</v>
+        <v>175</v>
       </c>
       <c r="D103" t="s">
         <v>32</v>
       </c>
       <c r="I103" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="J103" t="s">
-        <v>347</v>
+        <v>177</v>
       </c>
       <c r="K103" t="s">
         <v>35</v>
       </c>
       <c r="L103" t="s">
-        <v>348</v>
+        <v>178</v>
       </c>
       <c r="M103" t="s">
-        <v>349</v>
+        <v>179</v>
       </c>
       <c r="N103" t="s">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="O103" t="s">
         <v>39</v>
@@ -10505,14 +10616,8 @@
       <c r="S103" t="s">
         <v>43</v>
       </c>
-      <c r="T103" t="s">
-        <v>67</v>
-      </c>
-      <c r="U103" t="s">
-        <v>68</v>
-      </c>
       <c r="V103" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="W103" t="s">
         <v>45</v>
@@ -10532,34 +10637,34 @@
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B104" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C104" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D104" t="s">
         <v>32</v>
       </c>
       <c r="I104" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="J104" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K104" t="s">
         <v>35</v>
       </c>
       <c r="L104" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M104" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="N104" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="O104" t="s">
         <v>39</v>
@@ -10576,8 +10681,14 @@
       <c r="S104" t="s">
         <v>43</v>
       </c>
+      <c r="T104" t="s">
+        <v>67</v>
+      </c>
+      <c r="U104" t="s">
+        <v>68</v>
+      </c>
       <c r="V104" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="W104" t="s">
         <v>45</v>
@@ -10597,34 +10708,34 @@
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="B105" t="s">
-        <v>183</v>
+        <v>115</v>
       </c>
       <c r="C105" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
       <c r="D105" t="s">
         <v>32</v>
       </c>
       <c r="I105" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J105" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="K105" t="s">
         <v>35</v>
       </c>
       <c r="L105" t="s">
-        <v>186</v>
+        <v>118</v>
       </c>
       <c r="M105" t="s">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="N105" t="s">
-        <v>188</v>
+        <v>120</v>
       </c>
       <c r="O105" t="s">
         <v>39</v>
@@ -10668,34 +10779,34 @@
     </row>
     <row r="106" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C106" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D106" t="s">
         <v>32</v>
       </c>
       <c r="I106" t="s">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="J106" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="K106" t="s">
         <v>35</v>
       </c>
       <c r="L106" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="M106" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="N106" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="O106" t="s">
         <v>39</v>
@@ -10719,7 +10830,7 @@
         <v>68</v>
       </c>
       <c r="V106" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="W106" t="s">
         <v>45</v>
@@ -10739,34 +10850,34 @@
     </row>
     <row r="107" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>139</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s">
-        <v>140</v>
+        <v>334</v>
       </c>
       <c r="C107" t="s">
-        <v>141</v>
+        <v>335</v>
       </c>
       <c r="D107" t="s">
         <v>32</v>
       </c>
       <c r="I107" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="J107" t="s">
-        <v>143</v>
+        <v>336</v>
       </c>
       <c r="K107" t="s">
         <v>35</v>
       </c>
       <c r="L107" t="s">
-        <v>144</v>
+        <v>337</v>
       </c>
       <c r="M107" t="s">
-        <v>145</v>
+        <v>338</v>
       </c>
       <c r="N107" t="s">
-        <v>146</v>
+        <v>339</v>
       </c>
       <c r="O107" t="s">
         <v>39</v>
@@ -10790,7 +10901,7 @@
         <v>68</v>
       </c>
       <c r="V107" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="W107" t="s">
         <v>45</v>
@@ -10810,34 +10921,34 @@
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>333</v>
+        <v>61</v>
       </c>
       <c r="B108" t="s">
-        <v>334</v>
+        <v>62</v>
       </c>
       <c r="C108" t="s">
-        <v>335</v>
+        <v>63</v>
       </c>
       <c r="D108" t="s">
         <v>32</v>
       </c>
       <c r="I108" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="J108" t="s">
-        <v>336</v>
+        <v>34</v>
       </c>
       <c r="K108" t="s">
         <v>35</v>
       </c>
       <c r="L108" t="s">
-        <v>337</v>
+        <v>64</v>
       </c>
       <c r="M108" t="s">
-        <v>338</v>
+        <v>65</v>
       </c>
       <c r="N108" t="s">
-        <v>339</v>
+        <v>66</v>
       </c>
       <c r="O108" t="s">
         <v>39</v>
@@ -10861,7 +10972,7 @@
         <v>68</v>
       </c>
       <c r="V108" t="s">
-        <v>411</v>
+        <v>69</v>
       </c>
       <c r="W108" t="s">
         <v>45</v>
@@ -10870,10 +10981,10 @@
         <v>70</v>
       </c>
       <c r="Y108" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Z108" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AA108" t="s">
         <v>49</v>
@@ -10881,13 +10992,13 @@
     </row>
     <row r="109" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>61</v>
+        <v>304</v>
       </c>
       <c r="B109" t="s">
-        <v>62</v>
+        <v>305</v>
       </c>
       <c r="C109" t="s">
-        <v>63</v>
+        <v>306</v>
       </c>
       <c r="D109" t="s">
         <v>32</v>
@@ -10902,13 +11013,13 @@
         <v>35</v>
       </c>
       <c r="L109" t="s">
-        <v>64</v>
+        <v>307</v>
       </c>
       <c r="M109" t="s">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="N109" t="s">
-        <v>66</v>
+        <v>309</v>
       </c>
       <c r="O109" t="s">
         <v>39</v>
@@ -10925,14 +11036,8 @@
       <c r="S109" t="s">
         <v>43</v>
       </c>
-      <c r="T109" t="s">
-        <v>67</v>
-      </c>
-      <c r="U109" t="s">
-        <v>68</v>
-      </c>
       <c r="V109" t="s">
-        <v>69</v>
+        <v>310</v>
       </c>
       <c r="W109" t="s">
         <v>45</v>
@@ -10952,34 +11057,34 @@
     </row>
     <row r="110" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B110" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C110" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D110" t="s">
         <v>32</v>
       </c>
       <c r="I110" t="s">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="J110" t="s">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="K110" t="s">
         <v>35</v>
       </c>
       <c r="L110" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="M110" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="N110" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="O110" t="s">
         <v>39</v>
@@ -10997,7 +11102,7 @@
         <v>43</v>
       </c>
       <c r="V110" t="s">
-        <v>310</v>
+        <v>359</v>
       </c>
       <c r="W110" t="s">
         <v>45</v>
@@ -11017,34 +11122,34 @@
     </row>
     <row r="111" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>311</v>
+        <v>50</v>
       </c>
       <c r="B111" t="s">
-        <v>312</v>
+        <v>51</v>
       </c>
       <c r="C111" t="s">
-        <v>313</v>
+        <v>52</v>
       </c>
       <c r="D111" t="s">
         <v>32</v>
       </c>
       <c r="I111" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="J111" t="s">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="K111" t="s">
         <v>35</v>
       </c>
       <c r="L111" t="s">
-        <v>314</v>
+        <v>54</v>
       </c>
       <c r="M111" t="s">
-        <v>315</v>
+        <v>55</v>
       </c>
       <c r="N111" t="s">
-        <v>316</v>
+        <v>56</v>
       </c>
       <c r="O111" t="s">
         <v>39</v>
@@ -11062,7 +11167,7 @@
         <v>43</v>
       </c>
       <c r="V111" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="W111" t="s">
         <v>45</v>
@@ -11082,13 +11187,13 @@
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>50</v>
+        <v>161</v>
       </c>
       <c r="B112" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="C112" t="s">
-        <v>52</v>
+        <v>163</v>
       </c>
       <c r="D112" t="s">
         <v>32</v>
@@ -11097,19 +11202,19 @@
         <v>33</v>
       </c>
       <c r="J112" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="K112" t="s">
         <v>35</v>
       </c>
       <c r="L112" t="s">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="M112" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="N112" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="O112" t="s">
         <v>39</v>
@@ -11127,7 +11232,7 @@
         <v>43</v>
       </c>
       <c r="V112" t="s">
-        <v>363</v>
+        <v>404</v>
       </c>
       <c r="W112" t="s">
         <v>45</v>
@@ -11147,34 +11252,34 @@
     </row>
     <row r="113" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>161</v>
+        <v>255</v>
       </c>
       <c r="B113" t="s">
-        <v>162</v>
+        <v>256</v>
       </c>
       <c r="C113" t="s">
-        <v>163</v>
+        <v>257</v>
       </c>
       <c r="D113" t="s">
         <v>32</v>
       </c>
       <c r="I113" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="J113" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="K113" t="s">
         <v>35</v>
       </c>
       <c r="L113" t="s">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="M113" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="N113" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="O113" t="s">
         <v>39</v>
@@ -11191,8 +11296,14 @@
       <c r="S113" t="s">
         <v>43</v>
       </c>
+      <c r="T113" t="s">
+        <v>67</v>
+      </c>
+      <c r="U113" t="s">
+        <v>68</v>
+      </c>
       <c r="V113" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="W113" t="s">
         <v>45</v>
@@ -11212,34 +11323,34 @@
     </row>
     <row r="114" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="B114" t="s">
-        <v>256</v>
+        <v>78</v>
       </c>
       <c r="C114" t="s">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="D114" t="s">
         <v>32</v>
       </c>
       <c r="I114" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J114" t="s">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="K114" t="s">
         <v>35</v>
       </c>
       <c r="L114" t="s">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="M114" t="s">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="N114" t="s">
-        <v>260</v>
+        <v>84</v>
       </c>
       <c r="O114" t="s">
         <v>39</v>
@@ -11283,34 +11394,34 @@
     </row>
     <row r="115" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="C115" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="D115" t="s">
         <v>32</v>
       </c>
       <c r="I115" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J115" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="K115" t="s">
         <v>35</v>
       </c>
       <c r="L115" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="M115" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="N115" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="O115" t="s">
         <v>39</v>
@@ -11334,7 +11445,7 @@
         <v>68</v>
       </c>
       <c r="V115" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="W115" t="s">
         <v>45</v>
@@ -11354,13 +11465,13 @@
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C116" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D116" t="s">
         <v>32</v>
@@ -11369,19 +11480,19 @@
         <v>100</v>
       </c>
       <c r="J116" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K116" t="s">
         <v>35</v>
       </c>
       <c r="L116" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="M116" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="N116" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="O116" t="s">
         <v>39</v>
@@ -11398,14 +11509,8 @@
       <c r="S116" t="s">
         <v>43</v>
       </c>
-      <c r="T116" t="s">
-        <v>67</v>
-      </c>
-      <c r="U116" t="s">
-        <v>68</v>
-      </c>
       <c r="V116" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="W116" t="s">
         <v>45</v>
@@ -11425,34 +11530,34 @@
     </row>
     <row r="117" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="C117" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="D117" t="s">
         <v>32</v>
       </c>
       <c r="I117" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J117" t="s">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="K117" t="s">
         <v>35</v>
       </c>
       <c r="L117" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="M117" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="N117" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="O117" t="s">
         <v>39</v>
@@ -11469,8 +11574,14 @@
       <c r="S117" t="s">
         <v>43</v>
       </c>
+      <c r="T117" t="s">
+        <v>67</v>
+      </c>
+      <c r="U117" t="s">
+        <v>68</v>
+      </c>
       <c r="V117" t="s">
-        <v>420</v>
+        <v>74</v>
       </c>
       <c r="W117" t="s">
         <v>45</v>
@@ -11479,10 +11590,10 @@
         <v>70</v>
       </c>
       <c r="Y117" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="Z117" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="AA117" t="s">
         <v>49</v>
@@ -11490,34 +11601,34 @@
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>29</v>
+        <v>198</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>199</v>
       </c>
       <c r="C118" t="s">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="D118" t="s">
         <v>32</v>
       </c>
       <c r="I118" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="J118" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="K118" t="s">
         <v>35</v>
       </c>
       <c r="L118" t="s">
-        <v>71</v>
+        <v>201</v>
       </c>
       <c r="M118" t="s">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="N118" t="s">
-        <v>73</v>
+        <v>203</v>
       </c>
       <c r="O118" t="s">
         <v>39</v>
@@ -11541,7 +11652,7 @@
         <v>68</v>
       </c>
       <c r="V118" t="s">
-        <v>74</v>
+        <v>342</v>
       </c>
       <c r="W118" t="s">
         <v>45</v>
@@ -11561,34 +11672,31 @@
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B119" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C119" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D119" t="s">
         <v>32</v>
       </c>
       <c r="I119" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="J119" t="s">
-        <v>81</v>
-      </c>
-      <c r="K119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L119" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="M119" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="N119" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="O119" t="s">
         <v>39</v>
@@ -11612,51 +11720,54 @@
         <v>68</v>
       </c>
       <c r="V119" t="s">
-        <v>342</v>
+        <v>216</v>
       </c>
       <c r="W119" t="s">
         <v>45</v>
       </c>
       <c r="X119" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="Y119" t="s">
-        <v>75</v>
+        <v>214</v>
       </c>
       <c r="Z119" t="s">
-        <v>76</v>
+        <v>217</v>
       </c>
       <c r="AA119" t="s">
-        <v>49</v>
+        <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>207</v>
+        <v>148</v>
       </c>
       <c r="B120" t="s">
-        <v>208</v>
+        <v>149</v>
       </c>
       <c r="C120" t="s">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="D120" t="s">
         <v>32</v>
       </c>
       <c r="I120" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="J120" t="s">
-        <v>34</v>
+        <v>152</v>
+      </c>
+      <c r="K120" t="s">
+        <v>35</v>
       </c>
       <c r="L120" t="s">
-        <v>210</v>
+        <v>153</v>
       </c>
       <c r="M120" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="N120" t="s">
-        <v>212</v>
+        <v>155</v>
       </c>
       <c r="O120" t="s">
         <v>39</v>
@@ -11673,14 +11784,8 @@
       <c r="S120" t="s">
         <v>43</v>
       </c>
-      <c r="T120" t="s">
-        <v>67</v>
-      </c>
-      <c r="U120" t="s">
-        <v>68</v>
-      </c>
       <c r="V120" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="W120" t="s">
         <v>45</v>
@@ -11689,45 +11794,45 @@
         <v>130</v>
       </c>
       <c r="Y120" t="s">
-        <v>214</v>
+        <v>47</v>
       </c>
       <c r="Z120" t="s">
-        <v>217</v>
+        <v>48</v>
       </c>
       <c r="AA120" t="s">
-        <v>218</v>
+        <v>49</v>
       </c>
     </row>
     <row r="121" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>148</v>
+        <v>230</v>
       </c>
       <c r="B121" t="s">
-        <v>149</v>
+        <v>231</v>
       </c>
       <c r="C121" t="s">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="D121" t="s">
         <v>32</v>
       </c>
       <c r="I121" t="s">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="J121" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="K121" t="s">
         <v>35</v>
       </c>
       <c r="L121" t="s">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="M121" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="N121" t="s">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="O121" t="s">
         <v>39</v>
@@ -11744,8 +11849,14 @@
       <c r="S121" t="s">
         <v>43</v>
       </c>
+      <c r="T121" t="s">
+        <v>67</v>
+      </c>
+      <c r="U121" t="s">
+        <v>68</v>
+      </c>
       <c r="V121" t="s">
-        <v>156</v>
+        <v>236</v>
       </c>
       <c r="W121" t="s">
         <v>45</v>
@@ -11765,34 +11876,34 @@
     </row>
     <row r="122" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="B122" t="s">
-        <v>231</v>
+        <v>91</v>
       </c>
       <c r="C122" t="s">
-        <v>232</v>
+        <v>92</v>
       </c>
       <c r="D122" t="s">
         <v>32</v>
       </c>
       <c r="I122" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="J122" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="K122" t="s">
         <v>35</v>
       </c>
       <c r="L122" t="s">
-        <v>233</v>
+        <v>93</v>
       </c>
       <c r="M122" t="s">
-        <v>234</v>
+        <v>94</v>
       </c>
       <c r="N122" t="s">
-        <v>235</v>
+        <v>95</v>
       </c>
       <c r="O122" t="s">
         <v>39</v>
@@ -11816,7 +11927,7 @@
         <v>68</v>
       </c>
       <c r="V122" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="W122" t="s">
         <v>45</v>
@@ -11836,34 +11947,34 @@
     </row>
     <row r="123" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="B123" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="C123" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="D123" t="s">
         <v>32</v>
       </c>
       <c r="I123" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="J123" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="K123" t="s">
         <v>35</v>
       </c>
       <c r="L123" t="s">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="M123" t="s">
-        <v>94</v>
+        <v>194</v>
       </c>
       <c r="N123" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="O123" t="s">
         <v>39</v>
@@ -11880,14 +11991,8 @@
       <c r="S123" t="s">
         <v>43</v>
       </c>
-      <c r="T123" t="s">
-        <v>67</v>
-      </c>
-      <c r="U123" t="s">
-        <v>68</v>
-      </c>
       <c r="V123" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="W123" t="s">
         <v>45</v>
@@ -11907,13 +12012,13 @@
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="B124" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="C124" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
       <c r="D124" t="s">
         <v>32</v>
@@ -11922,19 +12027,19 @@
         <v>33</v>
       </c>
       <c r="J124" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="K124" t="s">
         <v>35</v>
       </c>
       <c r="L124" t="s">
-        <v>193</v>
+        <v>118</v>
       </c>
       <c r="M124" t="s">
-        <v>194</v>
+        <v>119</v>
       </c>
       <c r="N124" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="O124" t="s">
         <v>39</v>
@@ -11951,8 +12056,14 @@
       <c r="S124" t="s">
         <v>43</v>
       </c>
+      <c r="T124" t="s">
+        <v>67</v>
+      </c>
+      <c r="U124" t="s">
+        <v>68</v>
+      </c>
       <c r="V124" t="s">
-        <v>272</v>
+        <v>325</v>
       </c>
       <c r="W124" t="s">
         <v>45</v>
@@ -11972,34 +12083,34 @@
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B125" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="C125" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="D125" t="s">
         <v>32</v>
       </c>
       <c r="I125" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="J125" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="K125" t="s">
         <v>35</v>
       </c>
       <c r="L125" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="M125" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="N125" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="O125" t="s">
         <v>39</v>
@@ -12023,7 +12134,7 @@
         <v>68</v>
       </c>
       <c r="V125" t="s">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="W125" t="s">
         <v>45</v>
@@ -12043,34 +12154,34 @@
     </row>
     <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>97</v>
+        <v>333</v>
       </c>
       <c r="B126" t="s">
-        <v>98</v>
+        <v>334</v>
       </c>
       <c r="C126" t="s">
-        <v>99</v>
+        <v>335</v>
       </c>
       <c r="D126" t="s">
         <v>32</v>
       </c>
       <c r="I126" t="s">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="J126" t="s">
-        <v>101</v>
+        <v>336</v>
       </c>
       <c r="K126" t="s">
         <v>35</v>
       </c>
       <c r="L126" t="s">
-        <v>102</v>
+        <v>337</v>
       </c>
       <c r="M126" t="s">
-        <v>103</v>
+        <v>338</v>
       </c>
       <c r="N126" t="s">
-        <v>104</v>
+        <v>339</v>
       </c>
       <c r="O126" t="s">
         <v>39</v>
@@ -12094,7 +12205,7 @@
         <v>68</v>
       </c>
       <c r="V126" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="W126" t="s">
         <v>45</v>
@@ -12114,34 +12225,34 @@
     </row>
     <row r="127" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>333</v>
+        <v>139</v>
       </c>
       <c r="B127" t="s">
-        <v>334</v>
+        <v>140</v>
       </c>
       <c r="C127" t="s">
-        <v>335</v>
+        <v>141</v>
       </c>
       <c r="D127" t="s">
         <v>32</v>
       </c>
       <c r="I127" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="J127" t="s">
-        <v>336</v>
+        <v>143</v>
       </c>
       <c r="K127" t="s">
         <v>35</v>
       </c>
       <c r="L127" t="s">
-        <v>337</v>
+        <v>144</v>
       </c>
       <c r="M127" t="s">
-        <v>338</v>
+        <v>145</v>
       </c>
       <c r="N127" t="s">
-        <v>339</v>
+        <v>146</v>
       </c>
       <c r="O127" t="s">
         <v>39</v>
@@ -12165,7 +12276,7 @@
         <v>68</v>
       </c>
       <c r="V127" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="W127" t="s">
         <v>45</v>
@@ -12185,34 +12296,34 @@
     </row>
     <row r="128" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="B128" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="C128" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="D128" t="s">
         <v>32</v>
       </c>
       <c r="I128" t="s">
-        <v>142</v>
+        <v>222</v>
       </c>
       <c r="J128" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="K128" t="s">
         <v>35</v>
       </c>
       <c r="L128" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="M128" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="N128" t="s">
-        <v>146</v>
+        <v>226</v>
       </c>
       <c r="O128" t="s">
         <v>39</v>
@@ -12229,14 +12340,8 @@
       <c r="S128" t="s">
         <v>43</v>
       </c>
-      <c r="T128" t="s">
-        <v>67</v>
-      </c>
-      <c r="U128" t="s">
-        <v>68</v>
-      </c>
       <c r="V128" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="W128" t="s">
         <v>45</v>
@@ -12256,34 +12361,34 @@
     </row>
     <row r="129" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>219</v>
+        <v>285</v>
       </c>
       <c r="B129" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="C129" t="s">
-        <v>221</v>
+        <v>287</v>
       </c>
       <c r="D129" t="s">
         <v>32</v>
       </c>
       <c r="I129" t="s">
-        <v>222</v>
+        <v>100</v>
       </c>
       <c r="J129" t="s">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="K129" t="s">
         <v>35</v>
       </c>
       <c r="L129" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="M129" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="N129" t="s">
-        <v>226</v>
+        <v>290</v>
       </c>
       <c r="O129" t="s">
         <v>39</v>
@@ -12301,7 +12406,7 @@
         <v>43</v>
       </c>
       <c r="V129" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="W129" t="s">
         <v>45</v>
@@ -12321,13 +12426,13 @@
     </row>
     <row r="130" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>285</v>
+        <v>106</v>
       </c>
       <c r="B130" t="s">
-        <v>286</v>
+        <v>107</v>
       </c>
       <c r="C130" t="s">
-        <v>287</v>
+        <v>108</v>
       </c>
       <c r="D130" t="s">
         <v>32</v>
@@ -12336,19 +12441,19 @@
         <v>100</v>
       </c>
       <c r="J130" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K130" t="s">
         <v>35</v>
       </c>
       <c r="L130" t="s">
-        <v>288</v>
+        <v>110</v>
       </c>
       <c r="M130" t="s">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="N130" t="s">
-        <v>290</v>
+        <v>112</v>
       </c>
       <c r="O130" t="s">
         <v>39</v>
@@ -12365,8 +12470,14 @@
       <c r="S130" t="s">
         <v>43</v>
       </c>
+      <c r="T130" t="s">
+        <v>67</v>
+      </c>
+      <c r="U130" t="s">
+        <v>68</v>
+      </c>
       <c r="V130" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="W130" t="s">
         <v>45</v>
@@ -12386,34 +12497,34 @@
     </row>
     <row r="131" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>106</v>
+        <v>344</v>
       </c>
       <c r="B131" t="s">
-        <v>107</v>
+        <v>345</v>
       </c>
       <c r="C131" t="s">
-        <v>108</v>
+        <v>346</v>
       </c>
       <c r="D131" t="s">
         <v>32</v>
       </c>
       <c r="I131" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="J131" t="s">
-        <v>109</v>
+        <v>347</v>
       </c>
       <c r="K131" t="s">
         <v>35</v>
       </c>
       <c r="L131" t="s">
-        <v>110</v>
+        <v>348</v>
       </c>
       <c r="M131" t="s">
-        <v>111</v>
+        <v>349</v>
       </c>
       <c r="N131" t="s">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="O131" t="s">
         <v>39</v>
@@ -12437,7 +12548,7 @@
         <v>68</v>
       </c>
       <c r="V131" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="W131" t="s">
         <v>45</v>
@@ -12457,34 +12568,34 @@
     </row>
     <row r="132" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>344</v>
+        <v>274</v>
       </c>
       <c r="B132" t="s">
-        <v>345</v>
+        <v>275</v>
       </c>
       <c r="C132" t="s">
-        <v>346</v>
+        <v>276</v>
       </c>
       <c r="D132" t="s">
         <v>32</v>
       </c>
       <c r="I132" t="s">
-        <v>222</v>
+        <v>277</v>
       </c>
       <c r="J132" t="s">
-        <v>347</v>
+        <v>278</v>
       </c>
       <c r="K132" t="s">
         <v>35</v>
       </c>
       <c r="L132" t="s">
-        <v>348</v>
+        <v>279</v>
       </c>
       <c r="M132" t="s">
-        <v>349</v>
+        <v>280</v>
       </c>
       <c r="N132" t="s">
-        <v>350</v>
+        <v>281</v>
       </c>
       <c r="O132" t="s">
         <v>39</v>
@@ -12508,7 +12619,7 @@
         <v>68</v>
       </c>
       <c r="V132" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="W132" t="s">
         <v>45</v>
@@ -12528,34 +12639,34 @@
     </row>
     <row r="133" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>274</v>
+        <v>182</v>
       </c>
       <c r="B133" t="s">
-        <v>275</v>
+        <v>183</v>
       </c>
       <c r="C133" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="D133" t="s">
         <v>32</v>
       </c>
       <c r="I133" t="s">
-        <v>277</v>
+        <v>100</v>
       </c>
       <c r="J133" t="s">
-        <v>278</v>
+        <v>185</v>
       </c>
       <c r="K133" t="s">
         <v>35</v>
       </c>
       <c r="L133" t="s">
-        <v>279</v>
+        <v>186</v>
       </c>
       <c r="M133" t="s">
-        <v>280</v>
+        <v>187</v>
       </c>
       <c r="N133" t="s">
-        <v>281</v>
+        <v>188</v>
       </c>
       <c r="O133" t="s">
         <v>39</v>
@@ -12579,7 +12690,7 @@
         <v>68</v>
       </c>
       <c r="V133" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="W133" t="s">
         <v>45</v>
@@ -12599,34 +12710,34 @@
     </row>
     <row r="134" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B134" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C134" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D134" t="s">
         <v>32</v>
       </c>
       <c r="I134" t="s">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="J134" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="K134" t="s">
         <v>35</v>
       </c>
       <c r="L134" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M134" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N134" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="O134" t="s">
         <v>39</v>
@@ -12643,14 +12754,8 @@
       <c r="S134" t="s">
         <v>43</v>
       </c>
-      <c r="T134" t="s">
-        <v>67</v>
-      </c>
-      <c r="U134" t="s">
-        <v>68</v>
-      </c>
       <c r="V134" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="W134" t="s">
         <v>45</v>
@@ -12670,34 +12775,34 @@
     </row>
     <row r="135" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="B135" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="C135" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="D135" t="s">
         <v>32</v>
       </c>
       <c r="I135" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="J135" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="K135" t="s">
         <v>35</v>
       </c>
       <c r="L135" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="M135" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="N135" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="O135" t="s">
         <v>39</v>
@@ -12714,8 +12819,14 @@
       <c r="S135" t="s">
         <v>43</v>
       </c>
+      <c r="T135" t="s">
+        <v>67</v>
+      </c>
+      <c r="U135" t="s">
+        <v>68</v>
+      </c>
       <c r="V135" t="s">
-        <v>440</v>
+        <v>129</v>
       </c>
       <c r="W135" t="s">
         <v>45</v>
@@ -12724,10 +12835,10 @@
         <v>130</v>
       </c>
       <c r="Y135" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Z135" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AA135" t="s">
         <v>49</v>
@@ -12735,13 +12846,13 @@
     </row>
     <row r="136" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B136" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C136" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D136" t="s">
         <v>32</v>
@@ -12750,19 +12861,19 @@
         <v>100</v>
       </c>
       <c r="J136" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K136" t="s">
         <v>35</v>
       </c>
       <c r="L136" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="M136" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="N136" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="O136" t="s">
         <v>39</v>
@@ -12779,14 +12890,8 @@
       <c r="S136" t="s">
         <v>43</v>
       </c>
-      <c r="T136" t="s">
-        <v>67</v>
-      </c>
-      <c r="U136" t="s">
-        <v>68</v>
-      </c>
       <c r="V136" t="s">
-        <v>129</v>
+        <v>243</v>
       </c>
       <c r="W136" t="s">
         <v>45</v>
@@ -12806,34 +12911,34 @@
     </row>
     <row r="137" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="B137" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="C137" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="D137" t="s">
         <v>32</v>
       </c>
       <c r="I137" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J137" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="K137" t="s">
         <v>35</v>
       </c>
       <c r="L137" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="M137" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="N137" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="O137" t="s">
         <v>39</v>
@@ -12850,8 +12955,14 @@
       <c r="S137" t="s">
         <v>43</v>
       </c>
+      <c r="T137" t="s">
+        <v>67</v>
+      </c>
+      <c r="U137" t="s">
+        <v>68</v>
+      </c>
       <c r="V137" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="W137" t="s">
         <v>45</v>
@@ -12871,34 +12982,34 @@
     </row>
     <row r="138" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="B138" t="s">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="C138" t="s">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="D138" t="s">
         <v>32</v>
       </c>
       <c r="I138" t="s">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="J138" t="s">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="K138" t="s">
         <v>35</v>
       </c>
       <c r="L138" t="s">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="M138" t="s">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="N138" t="s">
-        <v>84</v>
+        <v>316</v>
       </c>
       <c r="O138" t="s">
         <v>39</v>
@@ -12915,14 +13026,8 @@
       <c r="S138" t="s">
         <v>43</v>
       </c>
-      <c r="T138" t="s">
-        <v>67</v>
-      </c>
-      <c r="U138" t="s">
-        <v>68</v>
-      </c>
       <c r="V138" t="s">
-        <v>270</v>
+        <v>352</v>
       </c>
       <c r="W138" t="s">
         <v>45</v>
@@ -12942,34 +13047,34 @@
     </row>
     <row r="139" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="B139" t="s">
-        <v>312</v>
+        <v>256</v>
       </c>
       <c r="C139" t="s">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="D139" t="s">
         <v>32</v>
       </c>
       <c r="I139" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="J139" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K139" t="s">
         <v>35</v>
       </c>
       <c r="L139" t="s">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="M139" t="s">
-        <v>315</v>
+        <v>259</v>
       </c>
       <c r="N139" t="s">
-        <v>316</v>
+        <v>260</v>
       </c>
       <c r="O139" t="s">
         <v>39</v>
@@ -12986,8 +13091,14 @@
       <c r="S139" t="s">
         <v>43</v>
       </c>
+      <c r="T139" t="s">
+        <v>67</v>
+      </c>
+      <c r="U139" t="s">
+        <v>68</v>
+      </c>
       <c r="V139" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="W139" t="s">
         <v>45</v>
@@ -13007,34 +13118,34 @@
     </row>
     <row r="140" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="B140" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="C140" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="D140" t="s">
         <v>32</v>
       </c>
       <c r="I140" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J140" t="s">
-        <v>185</v>
+        <v>298</v>
       </c>
       <c r="K140" t="s">
         <v>35</v>
       </c>
       <c r="L140" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="M140" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="N140" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="O140" t="s">
         <v>39</v>
@@ -13058,7 +13169,7 @@
         <v>68</v>
       </c>
       <c r="V140" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="W140" t="s">
         <v>45</v>
@@ -13078,13 +13189,13 @@
     </row>
     <row r="141" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>295</v>
+        <v>61</v>
       </c>
       <c r="B141" t="s">
-        <v>296</v>
+        <v>62</v>
       </c>
       <c r="C141" t="s">
-        <v>297</v>
+        <v>63</v>
       </c>
       <c r="D141" t="s">
         <v>32</v>
@@ -13093,19 +13204,19 @@
         <v>33</v>
       </c>
       <c r="J141" t="s">
-        <v>298</v>
+        <v>34</v>
       </c>
       <c r="K141" t="s">
         <v>35</v>
       </c>
       <c r="L141" t="s">
-        <v>299</v>
+        <v>64</v>
       </c>
       <c r="M141" t="s">
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="N141" t="s">
-        <v>301</v>
+        <v>66</v>
       </c>
       <c r="O141" t="s">
         <v>39</v>
@@ -13129,7 +13240,7 @@
         <v>68</v>
       </c>
       <c r="V141" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W141" t="s">
         <v>45</v>
@@ -13149,13 +13260,13 @@
     </row>
     <row r="142" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B142" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C142" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D142" t="s">
         <v>32</v>
@@ -13164,19 +13275,19 @@
         <v>33</v>
       </c>
       <c r="J142" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="K142" t="s">
         <v>35</v>
       </c>
       <c r="L142" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="M142" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="N142" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="O142" t="s">
         <v>39</v>
@@ -13193,14 +13304,8 @@
       <c r="S142" t="s">
         <v>43</v>
       </c>
-      <c r="T142" t="s">
-        <v>67</v>
-      </c>
-      <c r="U142" t="s">
-        <v>68</v>
-      </c>
       <c r="V142" t="s">
-        <v>372</v>
+        <v>409</v>
       </c>
       <c r="W142" t="s">
         <v>45</v>
@@ -13220,13 +13325,13 @@
     </row>
     <row r="143" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>50</v>
+        <v>161</v>
       </c>
       <c r="B143" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="C143" t="s">
-        <v>52</v>
+        <v>163</v>
       </c>
       <c r="D143" t="s">
         <v>32</v>
@@ -13235,19 +13340,19 @@
         <v>33</v>
       </c>
       <c r="J143" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="K143" t="s">
         <v>35</v>
       </c>
       <c r="L143" t="s">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="M143" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="N143" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="O143" t="s">
         <v>39</v>
@@ -13265,7 +13370,7 @@
         <v>43</v>
       </c>
       <c r="V143" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="W143" t="s">
         <v>45</v>
@@ -13285,13 +13390,13 @@
     </row>
     <row r="144" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>161</v>
+        <v>304</v>
       </c>
       <c r="B144" t="s">
-        <v>162</v>
+        <v>305</v>
       </c>
       <c r="C144" t="s">
-        <v>163</v>
+        <v>306</v>
       </c>
       <c r="D144" t="s">
         <v>32</v>
@@ -13306,13 +13411,13 @@
         <v>35</v>
       </c>
       <c r="L144" t="s">
-        <v>164</v>
+        <v>307</v>
       </c>
       <c r="M144" t="s">
-        <v>165</v>
+        <v>308</v>
       </c>
       <c r="N144" t="s">
-        <v>166</v>
+        <v>309</v>
       </c>
       <c r="O144" t="s">
         <v>39</v>
@@ -13330,7 +13435,7 @@
         <v>43</v>
       </c>
       <c r="V144" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="W144" t="s">
         <v>45</v>
@@ -13350,34 +13455,34 @@
     </row>
     <row r="145" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>304</v>
+        <v>198</v>
       </c>
       <c r="B145" t="s">
-        <v>305</v>
+        <v>199</v>
       </c>
       <c r="C145" t="s">
-        <v>306</v>
+        <v>200</v>
       </c>
       <c r="D145" t="s">
         <v>32</v>
       </c>
       <c r="I145" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="J145" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="K145" t="s">
         <v>35</v>
       </c>
       <c r="L145" t="s">
-        <v>307</v>
+        <v>201</v>
       </c>
       <c r="M145" t="s">
-        <v>308</v>
+        <v>202</v>
       </c>
       <c r="N145" t="s">
-        <v>309</v>
+        <v>203</v>
       </c>
       <c r="O145" t="s">
         <v>39</v>
@@ -13394,8 +13499,14 @@
       <c r="S145" t="s">
         <v>43</v>
       </c>
+      <c r="T145" t="s">
+        <v>67</v>
+      </c>
+      <c r="U145" t="s">
+        <v>68</v>
+      </c>
       <c r="V145" t="s">
-        <v>441</v>
+        <v>399</v>
       </c>
       <c r="W145" t="s">
         <v>45</v>
@@ -13404,10 +13515,10 @@
         <v>130</v>
       </c>
       <c r="Y145" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="Z145" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="AA145" t="s">
         <v>49</v>
@@ -13415,34 +13526,34 @@
     </row>
     <row r="146" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>198</v>
+        <v>29</v>
       </c>
       <c r="B146" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="C146" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="D146" t="s">
         <v>32</v>
       </c>
       <c r="I146" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="J146" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="K146" t="s">
         <v>35</v>
       </c>
       <c r="L146" t="s">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="M146" t="s">
-        <v>202</v>
+        <v>72</v>
       </c>
       <c r="N146" t="s">
-        <v>203</v>
+        <v>73</v>
       </c>
       <c r="O146" t="s">
         <v>39</v>
@@ -13466,7 +13577,7 @@
         <v>68</v>
       </c>
       <c r="V146" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="W146" t="s">
         <v>45</v>
@@ -13486,34 +13597,34 @@
     </row>
     <row r="147" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>29</v>
+        <v>219</v>
       </c>
       <c r="B147" t="s">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="C147" t="s">
-        <v>31</v>
+        <v>221</v>
       </c>
       <c r="D147" t="s">
         <v>32</v>
       </c>
       <c r="I147" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="J147" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="K147" t="s">
         <v>35</v>
       </c>
       <c r="L147" t="s">
-        <v>71</v>
+        <v>224</v>
       </c>
       <c r="M147" t="s">
-        <v>72</v>
+        <v>225</v>
       </c>
       <c r="N147" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="O147" t="s">
         <v>39</v>
@@ -13530,61 +13641,55 @@
       <c r="S147" t="s">
         <v>43</v>
       </c>
-      <c r="T147" t="s">
-        <v>67</v>
-      </c>
-      <c r="U147" t="s">
-        <v>68</v>
-      </c>
       <c r="V147" t="s">
-        <v>421</v>
+        <v>227</v>
       </c>
       <c r="W147" t="s">
         <v>45</v>
       </c>
       <c r="X147" t="s">
-        <v>130</v>
+        <v>228</v>
       </c>
       <c r="Y147" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="Z147" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="AA147" t="s">
-        <v>49</v>
+        <v>215</v>
       </c>
     </row>
     <row r="148" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>219</v>
+        <v>50</v>
       </c>
       <c r="B148" t="s">
-        <v>220</v>
+        <v>51</v>
       </c>
       <c r="C148" t="s">
-        <v>221</v>
+        <v>52</v>
       </c>
       <c r="D148" t="s">
         <v>32</v>
       </c>
       <c r="I148" t="s">
-        <v>222</v>
+        <v>33</v>
       </c>
       <c r="J148" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="K148" t="s">
         <v>35</v>
       </c>
       <c r="L148" t="s">
-        <v>224</v>
+        <v>54</v>
       </c>
       <c r="M148" t="s">
-        <v>225</v>
+        <v>55</v>
       </c>
       <c r="N148" t="s">
-        <v>226</v>
+        <v>56</v>
       </c>
       <c r="O148" t="s">
         <v>39</v>
@@ -13602,7 +13707,7 @@
         <v>43</v>
       </c>
       <c r="V148" t="s">
-        <v>227</v>
+        <v>329</v>
       </c>
       <c r="W148" t="s">
         <v>45</v>
@@ -13611,24 +13716,24 @@
         <v>228</v>
       </c>
       <c r="Y148" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Z148" t="s">
         <v>60</v>
       </c>
       <c r="AA148" t="s">
-        <v>215</v>
+        <v>49</v>
       </c>
     </row>
     <row r="149" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>50</v>
+        <v>161</v>
       </c>
       <c r="B149" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="C149" t="s">
-        <v>52</v>
+        <v>163</v>
       </c>
       <c r="D149" t="s">
         <v>32</v>
@@ -13637,19 +13742,19 @@
         <v>33</v>
       </c>
       <c r="J149" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="K149" t="s">
         <v>35</v>
       </c>
       <c r="L149" t="s">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="M149" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="N149" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="O149" t="s">
         <v>39</v>
@@ -13667,7 +13772,7 @@
         <v>43</v>
       </c>
       <c r="V149" t="s">
-        <v>329</v>
+        <v>378</v>
       </c>
       <c r="W149" t="s">
         <v>45</v>
@@ -13679,79 +13784,14 @@
         <v>59</v>
       </c>
       <c r="Z149" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="AA149" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>161</v>
-      </c>
-      <c r="B150" t="s">
-        <v>162</v>
-      </c>
-      <c r="C150" t="s">
-        <v>163</v>
-      </c>
-      <c r="D150" t="s">
-        <v>32</v>
-      </c>
-      <c r="I150" t="s">
-        <v>33</v>
-      </c>
-      <c r="J150" t="s">
-        <v>34</v>
-      </c>
-      <c r="K150" t="s">
-        <v>35</v>
-      </c>
-      <c r="L150" t="s">
-        <v>164</v>
-      </c>
-      <c r="M150" t="s">
-        <v>165</v>
-      </c>
-      <c r="N150" t="s">
-        <v>166</v>
-      </c>
-      <c r="O150" t="s">
-        <v>39</v>
-      </c>
-      <c r="P150" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q150" t="s">
-        <v>41</v>
-      </c>
-      <c r="R150" t="s">
-        <v>42</v>
-      </c>
-      <c r="S150" t="s">
-        <v>43</v>
-      </c>
-      <c r="V150" t="s">
-        <v>383</v>
-      </c>
-      <c r="W150" t="s">
-        <v>45</v>
-      </c>
-      <c r="X150" t="s">
-        <v>228</v>
-      </c>
-      <c r="Y150" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z150" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA150" t="s">
         <v>215</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC150"/>
+  <autoFilter ref="A1:AC149"/>
   <sortState ref="A2:AC152">
     <sortCondition ref="X2:X152"/>
     <sortCondition ref="Y2:Y152"/>
@@ -13762,30 +13802,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG89"/>
+  <dimension ref="A1:AG95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -13800,13 +13840,13 @@
         <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>13</v>
@@ -13815,60 +13855,60 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>207</v>
@@ -13904,44 +13944,44 @@
         <v>40</v>
       </c>
       <c r="Q2" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="V2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AE2" s="2" t="s">
         <v>42</v>
@@ -13955,7 +13995,7 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>333</v>
@@ -13995,44 +14035,44 @@
         <v>40</v>
       </c>
       <c r="Q3" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="AB3" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="AE3" s="2" t="s">
         <v>42</v>
@@ -14046,7 +14086,7 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>190</v>
@@ -14086,44 +14126,44 @@
         <v>40</v>
       </c>
       <c r="Q4" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="Y4" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="S4" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="U4" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="AB4" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="AE4" s="2" t="s">
         <v>42</v>
@@ -14135,7 +14175,7 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>61</v>
@@ -14175,44 +14215,44 @@
         <v>40</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="Z5" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="AA5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB5" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="AE5" s="2" t="s">
         <v>42</v>
@@ -14226,7 +14266,7 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>182</v>
@@ -14266,36 +14306,36 @@
         <v>40</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
       <c r="Z6" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="AE6" s="2" t="s">
         <v>42</v>
@@ -14309,7 +14349,7 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>285</v>
@@ -14334,7 +14374,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>101</v>
@@ -14349,44 +14389,44 @@
         <v>40</v>
       </c>
       <c r="Q7" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="Y7" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="AA7" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>588</v>
-      </c>
       <c r="AB7" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>42</v>
@@ -14398,7 +14438,7 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>274</v>
@@ -14438,44 +14478,44 @@
         <v>40</v>
       </c>
       <c r="Q8" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="Y8" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T8" s="2" t="s">
+      <c r="AA8" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="U8" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="AB8" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="AE8" s="2" t="s">
         <v>42</v>
@@ -14489,7 +14529,7 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>311</v>
@@ -14529,42 +14569,42 @@
         <v>40</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="W9" s="2"/>
       <c r="X9" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="AE9" s="2" t="s">
         <v>42</v>
@@ -14576,7 +14616,7 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>131</v>
@@ -14616,44 +14656,44 @@
         <v>40</v>
       </c>
       <c r="Q10" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="Y10" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="Z10" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="S10" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T10" s="2" t="s">
+      <c r="AA10" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="U10" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>620</v>
-      </c>
       <c r="AB10" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AC10" s="2"/>
       <c r="AD10" s="2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="AE10" s="2" t="s">
         <v>42</v>
@@ -14665,7 +14705,7 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>114</v>
@@ -14705,42 +14745,42 @@
         <v>40</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="W11" s="2"/>
       <c r="X11" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="AE11" s="2" t="s">
         <v>42</v>
@@ -14754,7 +14794,7 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>139</v>
@@ -14794,44 +14834,44 @@
         <v>40</v>
       </c>
       <c r="Q12" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="Y12" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="Z12" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="AA12" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="S12" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>640</v>
-      </c>
       <c r="AB12" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" s="2" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="AE12" s="2" t="s">
         <v>42</v>
@@ -14845,7 +14885,7 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>77</v>
@@ -14885,44 +14925,44 @@
         <v>40</v>
       </c>
       <c r="Q13" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="Y13" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="Z13" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="AA13" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="S13" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="Z13" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="AA13" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="AB13" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="AE13" s="2" t="s">
         <v>42</v>
@@ -14936,7 +14976,7 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>198</v>
@@ -14976,44 +15016,44 @@
         <v>40</v>
       </c>
       <c r="Q14" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="Y14" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="Z14" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="S14" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="T14" s="2" t="s">
+      <c r="AA14" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="U14" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="AA14" s="2" t="s">
-        <v>661</v>
-      </c>
       <c r="AB14" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" s="2" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="AE14" s="2" t="s">
         <v>42</v>
@@ -15027,7 +15067,7 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>344</v>
@@ -15067,32 +15107,32 @@
         <v>40</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
       <c r="Z15" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
       <c r="AC15" s="2"/>
       <c r="AD15" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="AE15" s="2" t="s">
         <v>42</v>
@@ -15106,7 +15146,7 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>207</v>
@@ -15142,32 +15182,32 @@
         <v>40</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA16" s="2"/>
       <c r="AB16" s="2"/>
       <c r="AC16" s="2"/>
       <c r="AD16" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="AE16" s="2" t="s">
         <v>42</v>
@@ -15181,7 +15221,7 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>148</v>
@@ -15221,32 +15261,32 @@
         <v>40</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
       <c r="Z17" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="AE17" s="2" t="s">
         <v>42</v>
@@ -15258,7 +15298,7 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>139</v>
@@ -15298,32 +15338,32 @@
         <v>40</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
       <c r="Z18" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
       <c r="AC18" s="2"/>
       <c r="AD18" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="AE18" s="2" t="s">
         <v>42</v>
@@ -15337,7 +15377,7 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>285</v>
@@ -15362,7 +15402,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>101</v>
@@ -15377,32 +15417,32 @@
         <v>40</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
       <c r="Z19" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
       <c r="AC19" s="2"/>
       <c r="AD19" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="AE19" s="2" t="s">
         <v>42</v>
@@ -15414,7 +15454,7 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>61</v>
@@ -15454,32 +15494,32 @@
         <v>40</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
       <c r="Z20" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="AE20" s="2" t="s">
         <v>42</v>
@@ -15493,7 +15533,7 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>274</v>
@@ -15533,32 +15573,32 @@
         <v>40</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
       <c r="Z21" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA21" s="2"/>
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="AE21" s="2" t="s">
         <v>42</v>
@@ -15572,7 +15612,7 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>97</v>
@@ -15612,32 +15652,32 @@
         <v>40</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
       <c r="Z22" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA22" s="2"/>
       <c r="AB22" s="2"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="AE22" s="2" t="s">
         <v>42</v>
@@ -15651,7 +15691,7 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>173</v>
@@ -15660,7 +15700,7 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>174</v>
@@ -15689,32 +15729,32 @@
         <v>40</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
       <c r="Z23" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA23" s="2"/>
       <c r="AB23" s="2"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="AE23" s="2" t="s">
         <v>42</v>
@@ -15726,7 +15766,7 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>90</v>
@@ -15766,32 +15806,32 @@
         <v>40</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
       <c r="Z24" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="AE24" s="2" t="s">
         <v>42</v>
@@ -15805,7 +15845,7 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>295</v>
@@ -15845,32 +15885,32 @@
         <v>40</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
       <c r="Z25" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="2" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="AE25" s="2" t="s">
         <v>42</v>
@@ -15884,7 +15924,7 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>219</v>
@@ -15924,32 +15964,32 @@
         <v>40</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
       <c r="Z26" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA26" s="2"/>
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="AE26" s="2" t="s">
         <v>42</v>
@@ -15961,7 +16001,7 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>29</v>
@@ -16001,32 +16041,32 @@
         <v>40</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
       <c r="Z27" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="AE27" s="2" t="s">
         <v>42</v>
@@ -16038,7 +16078,7 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>106</v>
@@ -16078,32 +16118,32 @@
         <v>40</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
       <c r="Z28" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="AE28" s="2" t="s">
         <v>42</v>
@@ -16117,7 +16157,7 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>122</v>
@@ -16126,7 +16166,7 @@
         <v>35</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>123</v>
@@ -16155,32 +16195,32 @@
         <v>40</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="2"/>
       <c r="Z29" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA29" s="2"/>
       <c r="AB29" s="2"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="2" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="AE29" s="2" t="s">
         <v>42</v>
@@ -16194,7 +16234,7 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>90</v>
@@ -16234,32 +16274,32 @@
         <v>40</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
       <c r="Z30" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA30" s="2"/>
       <c r="AB30" s="2"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="2" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="AE30" s="2" t="s">
         <v>42</v>
@@ -16271,7 +16311,7 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>50</v>
@@ -16311,32 +16351,32 @@
         <v>40</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
       <c r="Z31" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA31" s="2"/>
       <c r="AB31" s="2"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="AE31" s="2" t="s">
         <v>42</v>
@@ -16348,7 +16388,7 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>255</v>
@@ -16388,32 +16428,32 @@
         <v>40</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
       <c r="Z32" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="2" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="AE32" s="2" t="s">
         <v>42</v>
@@ -16427,7 +16467,7 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>161</v>
@@ -16467,32 +16507,32 @@
         <v>40</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
       <c r="Y33" s="2"/>
       <c r="Z33" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA33" s="2"/>
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="AE33" s="2" t="s">
         <v>42</v>
@@ -16506,7 +16546,7 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>161</v>
@@ -16546,32 +16586,32 @@
         <v>40</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
       <c r="Y34" s="2"/>
       <c r="Z34" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA34" s="2"/>
       <c r="AB34" s="2"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="AE34" s="2" t="s">
         <v>42</v>
@@ -16583,7 +16623,7 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>230</v>
@@ -16623,32 +16663,32 @@
         <v>40</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
       <c r="Y35" s="2"/>
       <c r="Z35" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA35" s="2"/>
       <c r="AB35" s="2"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="AE35" s="2" t="s">
         <v>42</v>
@@ -16662,7 +16702,7 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>304</v>
@@ -16702,32 +16742,32 @@
         <v>40</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
       <c r="Y36" s="2"/>
       <c r="Z36" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AA36" s="2"/>
       <c r="AB36" s="2"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="AE36" s="2" t="s">
         <v>42</v>
@@ -16739,7 +16779,7 @@
     </row>
     <row r="37" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>161</v>
@@ -16775,25 +16815,25 @@
         <v>40</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U37" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z37" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z37" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD37" s="3" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="AE37" s="3" t="s">
         <v>42</v>
@@ -16804,7 +16844,7 @@
     </row>
     <row r="38" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>207</v>
@@ -16834,25 +16874,25 @@
         <v>40</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="Z38" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AD38" s="3" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="AE38" s="3" t="s">
         <v>42</v>
@@ -16866,7 +16906,7 @@
     </row>
     <row r="39" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>61</v>
@@ -16902,25 +16942,25 @@
         <v>40</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="U39" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z39" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z39" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD39" s="3" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="AE39" s="3" t="s">
         <v>42</v>
@@ -16934,7 +16974,7 @@
     </row>
     <row r="40" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>148</v>
@@ -16970,25 +17010,25 @@
         <v>40</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="U40" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z40" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z40" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD40" s="3" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="AE40" s="3" t="s">
         <v>42</v>
@@ -16999,7 +17039,7 @@
     </row>
     <row r="41" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>106</v>
@@ -17035,25 +17075,25 @@
         <v>40</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="U41" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z41" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD41" s="3" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="AE41" s="3" t="s">
         <v>42</v>
@@ -17067,7 +17107,7 @@
     </row>
     <row r="42" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>333</v>
@@ -17103,25 +17143,25 @@
         <v>40</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="U42" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z42" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD42" s="3" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>42</v>
@@ -17135,7 +17175,7 @@
     </row>
     <row r="43" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>219</v>
@@ -17171,25 +17211,25 @@
         <v>40</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="U43" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z43" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD43" s="3" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>42</v>
@@ -17200,7 +17240,7 @@
     </row>
     <row r="44" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>295</v>
@@ -17236,25 +17276,25 @@
         <v>40</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="U44" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z44" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD44" s="3" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="AE44" s="3" t="s">
         <v>42</v>
@@ -17268,7 +17308,7 @@
     </row>
     <row r="45" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>182</v>
@@ -17304,25 +17344,25 @@
         <v>40</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="U45" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z45" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD45" s="3" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>42</v>
@@ -17336,7 +17376,7 @@
     </row>
     <row r="46" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>190</v>
@@ -17372,25 +17412,25 @@
         <v>40</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="U46" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z46" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD46" s="3" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="AE46" s="3" t="s">
         <v>42</v>
@@ -17401,7 +17441,7 @@
     </row>
     <row r="47" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>122</v>
@@ -17410,7 +17450,7 @@
         <v>35</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>123</v>
@@ -17434,25 +17474,25 @@
         <v>40</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="U47" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z47" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD47" s="3" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>42</v>
@@ -17466,7 +17506,7 @@
     </row>
     <row r="48" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>97</v>
@@ -17502,25 +17542,25 @@
         <v>40</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="U48" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z48" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD48" s="3" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>42</v>
@@ -17534,7 +17574,7 @@
     </row>
     <row r="49" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>29</v>
@@ -17570,25 +17610,25 @@
         <v>40</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="U49" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z49" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD49" s="3" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>42</v>
@@ -17599,7 +17639,7 @@
     </row>
     <row r="50" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>344</v>
@@ -17635,25 +17675,25 @@
         <v>40</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="U50" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z50" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z50" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD50" s="3" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="AE50" s="3" t="s">
         <v>42</v>
@@ -17667,7 +17707,7 @@
     </row>
     <row r="51" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>114</v>
@@ -17703,25 +17743,25 @@
         <v>40</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="U51" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z51" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z51" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD51" s="3" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="AE51" s="3" t="s">
         <v>42</v>
@@ -17735,7 +17775,7 @@
     </row>
     <row r="52" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>90</v>
@@ -17771,25 +17811,25 @@
         <v>40</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="U52" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z52" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD52" s="3" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>42</v>
@@ -17803,7 +17843,7 @@
     </row>
     <row r="53" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>173</v>
@@ -17812,7 +17852,7 @@
         <v>35</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>174</v>
@@ -17836,25 +17876,25 @@
         <v>40</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="U53" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z53" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z53" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD53" s="3" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="AE53" s="3" t="s">
         <v>42</v>
@@ -17865,7 +17905,7 @@
     </row>
     <row r="54" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>311</v>
@@ -17901,25 +17941,25 @@
         <v>40</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="U54" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z54" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD54" s="3" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="AE54" s="3" t="s">
         <v>42</v>
@@ -17930,7 +17970,7 @@
     </row>
     <row r="55" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>198</v>
@@ -17966,25 +18006,25 @@
         <v>40</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="U55" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z55" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z55" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD55" s="3" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="AE55" s="3" t="s">
         <v>42</v>
@@ -17995,7 +18035,7 @@
     </row>
     <row r="56" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>131</v>
@@ -18031,25 +18071,25 @@
         <v>40</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="U56" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z56" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z56" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD56" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="AE56" s="3" t="s">
         <v>42</v>
@@ -18060,7 +18100,7 @@
     </row>
     <row r="57" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>50</v>
@@ -18096,25 +18136,25 @@
         <v>40</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="U57" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z57" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD57" s="3" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>42</v>
@@ -18125,7 +18165,7 @@
     </row>
     <row r="58" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>255</v>
@@ -18161,25 +18201,25 @@
         <v>40</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="U58" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z58" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD58" s="3" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>42</v>
@@ -18193,7 +18233,7 @@
     </row>
     <row r="59" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>161</v>
@@ -18229,25 +18269,25 @@
         <v>40</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="U59" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z59" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD59" s="3" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>42</v>
@@ -18261,7 +18301,7 @@
     </row>
     <row r="60" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>230</v>
@@ -18297,25 +18337,25 @@
         <v>40</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="U60" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z60" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD60" s="3" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="AE60" s="3" t="s">
         <v>42</v>
@@ -18329,7 +18369,7 @@
     </row>
     <row r="61" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>198</v>
@@ -18365,25 +18405,25 @@
         <v>40</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="U61" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z61" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z61" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD61" s="3" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="AE61" s="3" t="s">
         <v>42</v>
@@ -18397,7 +18437,7 @@
     </row>
     <row r="62" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>304</v>
@@ -18433,25 +18473,25 @@
         <v>40</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="U62" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z62" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="AD62" s="3" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>42</v>
@@ -18462,7 +18502,7 @@
     </row>
     <row r="63" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>304</v>
@@ -18498,51 +18538,51 @@
         <v>68</v>
       </c>
       <c r="Q63" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="R63" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="U63" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="V63" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="W63" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="X63" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="R63" s="3" t="s">
+      <c r="Y63" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="S63" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="T63" s="3" t="s">
+      <c r="Z63" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="U63" s="3" t="s">
+      <c r="AA63" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="V63" s="3" t="s">
+      <c r="AB63" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="AD63" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="W63" s="3" t="s">
+      <c r="AG63" s="3" t="s">
         <v>856</v>
-      </c>
-      <c r="X63" s="3" t="s">
-        <v>857</v>
-      </c>
-      <c r="Y63" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="Z63" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="AA63" s="3" t="s">
-        <v>860</v>
-      </c>
-      <c r="AB63" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="AD63" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="AG63" s="3" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="64" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>161</v>
@@ -18578,51 +18618,51 @@
         <v>68</v>
       </c>
       <c r="Q64" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="U64" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="V64" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="W64" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="X64" s="3" t="s">
         <v>864</v>
       </c>
-      <c r="R64" s="3" t="s">
+      <c r="Y64" s="3" t="s">
         <v>865</v>
       </c>
-      <c r="S64" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="T64" s="3" t="s">
+      <c r="Z64" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="U64" s="3" t="s">
+      <c r="AA64" s="3" t="s">
         <v>867</v>
       </c>
-      <c r="V64" s="3" t="s">
+      <c r="AB64" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="AD64" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="W64" s="3" t="s">
-        <v>869</v>
-      </c>
-      <c r="X64" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="Y64" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="Z64" s="3" t="s">
-        <v>872</v>
-      </c>
-      <c r="AA64" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="AB64" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="AD64" s="3" t="s">
-        <v>874</v>
-      </c>
       <c r="AG64" s="3" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
     </row>
     <row r="65" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>139</v>
@@ -18658,25 +18698,25 @@
         <v>40</v>
       </c>
       <c r="Q65" s="4" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="R65" s="4" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="S65" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T65" s="4" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="U65" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z65" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z65" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD65" s="4" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="AE65" s="4" t="s">
         <v>42</v>
@@ -18690,19 +18730,19 @@
     </row>
     <row r="66" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>277</v>
@@ -18711,7 +18751,7 @@
         <v>32</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="N66" s="4" t="s">
         <v>42</v>
@@ -18723,33 +18763,51 @@
         <v>68</v>
       </c>
       <c r="Q66" s="4" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="R66" s="4" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="S66" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T66" s="4" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="U66" s="4" t="s">
-        <v>887</v>
+        <v>881</v>
+      </c>
+      <c r="V66" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="W66" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="X66" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="Y66" s="4" t="s">
+        <v>1004</v>
       </c>
       <c r="Z66" s="4" t="s">
-        <v>475</v>
+        <v>1005</v>
+      </c>
+      <c r="AA66" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="AB66" s="4" t="s">
+        <v>532</v>
       </c>
       <c r="AD66" s="4" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="AG66" s="4" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
     </row>
     <row r="67" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>274</v>
@@ -18785,25 +18843,25 @@
         <v>40</v>
       </c>
       <c r="Q67" s="4" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="R67" s="4" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="S67" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T67" s="4" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="U67" s="4" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="Z67" s="4" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AD67" s="4" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="AE67" s="4" t="s">
         <v>42</v>
@@ -18817,7 +18875,7 @@
     </row>
     <row r="68" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>207</v>
@@ -18847,25 +18905,25 @@
         <v>40</v>
       </c>
       <c r="Q68" s="4" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="R68" s="4" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="S68" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T68" s="4" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="U68" s="4" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="Z68" s="4" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AD68" s="4" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="AE68" s="4" t="s">
         <v>42</v>
@@ -18879,7 +18937,7 @@
     </row>
     <row r="69" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>311</v>
@@ -18915,25 +18973,25 @@
         <v>40</v>
       </c>
       <c r="Q69" s="4" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="R69" s="4" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="S69" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T69" s="4" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="U69" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z69" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z69" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD69" s="4" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="AE69" s="4" t="s">
         <v>42</v>
@@ -18944,7 +19002,7 @@
     </row>
     <row r="70" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>285</v>
@@ -18965,7 +19023,7 @@
         <v>32</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M70" s="4" t="s">
         <v>101</v>
@@ -18980,25 +19038,25 @@
         <v>40</v>
       </c>
       <c r="Q70" s="4" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="R70" s="4" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="S70" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T70" s="4" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="U70" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z70" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z70" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD70" s="4" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="AE70" s="4" t="s">
         <v>42</v>
@@ -19009,7 +19067,7 @@
     </row>
     <row r="71" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>148</v>
@@ -19045,25 +19103,25 @@
         <v>40</v>
       </c>
       <c r="Q71" s="4" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="R71" s="4" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="S71" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T71" s="4" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="U71" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z71" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z71" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD71" s="4" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="AE71" s="4" t="s">
         <v>42</v>
@@ -19074,7 +19132,7 @@
     </row>
     <row r="72" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>219</v>
@@ -19110,25 +19168,25 @@
         <v>40</v>
       </c>
       <c r="Q72" s="4" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="R72" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="S72" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T72" s="4" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="U72" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z72" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z72" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD72" s="4" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="AE72" s="4" t="s">
         <v>42</v>
@@ -19139,7 +19197,7 @@
     </row>
     <row r="73" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>295</v>
@@ -19175,25 +19233,25 @@
         <v>40</v>
       </c>
       <c r="Q73" s="4" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="R73" s="4" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="S73" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T73" s="4" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="U73" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z73" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z73" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD73" s="4" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="AE73" s="4" t="s">
         <v>42</v>
@@ -19207,7 +19265,7 @@
     </row>
     <row r="74" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>190</v>
@@ -19243,25 +19301,25 @@
         <v>40</v>
       </c>
       <c r="Q74" s="4" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="R74" s="4" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="S74" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T74" s="4" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="U74" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z74" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z74" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD74" s="4" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="AE74" s="4" t="s">
         <v>42</v>
@@ -19272,7 +19330,7 @@
     </row>
     <row r="75" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>333</v>
@@ -19308,25 +19366,25 @@
         <v>40</v>
       </c>
       <c r="Q75" s="4" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="R75" s="4" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="S75" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T75" s="4" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="U75" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z75" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z75" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD75" s="4" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="AE75" s="4" t="s">
         <v>42</v>
@@ -19340,7 +19398,7 @@
     </row>
     <row r="76" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>173</v>
@@ -19349,7 +19407,7 @@
         <v>35</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>174</v>
@@ -19373,25 +19431,25 @@
         <v>40</v>
       </c>
       <c r="Q76" s="4" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="R76" s="4" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="S76" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T76" s="4" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="U76" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z76" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z76" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD76" s="4" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="AE76" s="4" t="s">
         <v>42</v>
@@ -19402,7 +19460,7 @@
     </row>
     <row r="77" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>249</v>
@@ -19438,25 +19496,43 @@
         <v>40</v>
       </c>
       <c r="Q77" s="4" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="R77" s="4" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="S77" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T77" s="4" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="U77" s="4" t="s">
-        <v>943</v>
+        <v>937</v>
+      </c>
+      <c r="V77" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="W77" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="X77" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="Y77" s="4" t="s">
+        <v>1010</v>
       </c>
       <c r="Z77" s="4" t="s">
-        <v>475</v>
+        <v>1011</v>
+      </c>
+      <c r="AA77" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="AB77" s="4" t="s">
+        <v>532</v>
       </c>
       <c r="AD77" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="AE77" s="4" t="s">
         <v>42</v>
@@ -19470,7 +19546,7 @@
     </row>
     <row r="78" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>114</v>
@@ -19506,25 +19582,25 @@
         <v>40</v>
       </c>
       <c r="Q78" s="4" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="R78" s="4" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="S78" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T78" s="4" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="U78" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z78" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z78" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD78" s="4" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="AE78" s="4" t="s">
         <v>42</v>
@@ -19538,7 +19614,7 @@
     </row>
     <row r="79" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>344</v>
@@ -19574,25 +19650,25 @@
         <v>40</v>
       </c>
       <c r="Q79" s="4" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="R79" s="4" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="S79" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T79" s="4" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="U79" s="4" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="Z79" s="4" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AD79" s="4" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="AE79" s="4" t="s">
         <v>42</v>
@@ -19606,7 +19682,7 @@
     </row>
     <row r="80" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>106</v>
@@ -19642,25 +19718,25 @@
         <v>40</v>
       </c>
       <c r="Q80" s="4" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="R80" s="4" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="S80" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T80" s="4" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="U80" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z80" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z80" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD80" s="4" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="AE80" s="4" t="s">
         <v>42</v>
@@ -19674,7 +19750,7 @@
     </row>
     <row r="81" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>29</v>
@@ -19710,25 +19786,25 @@
         <v>40</v>
       </c>
       <c r="Q81" s="4" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="R81" s="4" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="S81" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T81" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="U81" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z81" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z81" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD81" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="AE81" s="4" t="s">
         <v>42</v>
@@ -19739,7 +19815,7 @@
     </row>
     <row r="82" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>182</v>
@@ -19775,25 +19851,25 @@
         <v>40</v>
       </c>
       <c r="Q82" s="4" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="R82" s="4" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="S82" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T82" s="4" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="U82" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z82" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z82" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD82" s="4" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="AE82" s="4" t="s">
         <v>42</v>
@@ -19807,7 +19883,7 @@
     </row>
     <row r="83" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>263</v>
@@ -19843,25 +19919,25 @@
         <v>40</v>
       </c>
       <c r="Q83" s="4" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="R83" s="4" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="S83" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T83" s="4" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="U83" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z83" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z83" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD83" s="4" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="AE83" s="4" t="s">
         <v>42</v>
@@ -19875,7 +19951,7 @@
     </row>
     <row r="84" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>131</v>
@@ -19911,25 +19987,25 @@
         <v>40</v>
       </c>
       <c r="Q84" s="4" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="R84" s="4" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="S84" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T84" s="4" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="U84" s="4" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="Z84" s="4" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AD84" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="AE84" s="4" t="s">
         <v>42</v>
@@ -19940,7 +20016,7 @@
     </row>
     <row r="85" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>255</v>
@@ -19976,25 +20052,25 @@
         <v>40</v>
       </c>
       <c r="Q85" s="4" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="R85" s="4" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="S85" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T85" s="4" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="U85" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z85" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z85" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD85" s="4" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="AE85" s="4" t="s">
         <v>42</v>
@@ -20008,7 +20084,7 @@
     </row>
     <row r="86" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>50</v>
@@ -20044,25 +20120,25 @@
         <v>40</v>
       </c>
       <c r="Q86" s="4" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="R86" s="4" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="S86" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T86" s="4" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="U86" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z86" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z86" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD86" s="4" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="AE86" s="4" t="s">
         <v>42</v>
@@ -20073,7 +20149,7 @@
     </row>
     <row r="87" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>77</v>
@@ -20109,25 +20185,25 @@
         <v>40</v>
       </c>
       <c r="Q87" s="4" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="R87" s="4" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="S87" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T87" s="4" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="U87" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z87" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z87" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD87" s="4" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="AE87" s="4" t="s">
         <v>42</v>
@@ -20141,7 +20217,7 @@
     </row>
     <row r="88" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>161</v>
@@ -20177,25 +20253,25 @@
         <v>40</v>
       </c>
       <c r="Q88" s="4" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="R88" s="4" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="S88" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T88" s="4" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="U88" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z88" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z88" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD88" s="4" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="AE88" s="4" t="s">
         <v>42</v>
@@ -20209,7 +20285,7 @@
     </row>
     <row r="89" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>161</v>
@@ -20245,30 +20321,429 @@
         <v>40</v>
       </c>
       <c r="Q89" s="4" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="R89" s="4" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="S89" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="T89" s="4" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="U89" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z89" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="Z89" s="4" t="s">
-        <v>475</v>
-      </c>
       <c r="AD89" s="4" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="AE89" s="4" t="s">
         <v>42</v>
       </c>
       <c r="AF89" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="90" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M90" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="N90" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="P90" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q90" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="R90" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="S90" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="T90" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="U90" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z90" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="AD90" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AE90" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF90" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG90" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="91" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M91" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="N91" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="O91" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="P91" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q91" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="R91" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="S91" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="T91" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="U91" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="Z91" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="AD91" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AE91" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF91" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG91" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N92" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="O92" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="P92" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q92" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="R92" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="S92" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="T92" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="U92" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z92" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="AD92" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AE92" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF92" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG92" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="93" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N93" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="O93" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="P93" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q93" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="R93" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="S93" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="T93" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="U93" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="Z93" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="AD93" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AE93" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF93" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M94" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N94" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="O94" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="P94" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q94" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="R94" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="S94" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="T94" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="U94" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="Z94" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="AD94" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AE94" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF94" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG94" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="95" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N95" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="O95" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="P95" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q95" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="R95" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="S95" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="T95" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="U95" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z95" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="AD95" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AE95" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF95" s="4" t="s">
         <v>43</v>
       </c>
     </row>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="programacion" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5455" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5648" uniqueCount="1083">
   <si>
     <t>ID PDV</t>
   </si>
@@ -3138,6 +3138,141 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1007634699_DBD_INGRESO_PDV_62087_24_09_2026_11_44_08.jpg</t>
+  </si>
+  <si>
+    <t>7826171</t>
+  </si>
+  <si>
+    <t>4.657048333333334</t>
+  </si>
+  <si>
+    <t>-74.07242166666667</t>
+  </si>
+  <si>
+    <t>25/09/2026 08:22:36</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1000126464_DBD_INGRESO_PDV_2632_25_09_2026_08_22_31.jpg</t>
+  </si>
+  <si>
+    <t>7826187</t>
+  </si>
+  <si>
+    <t>2.9536000000000002</t>
+  </si>
+  <si>
+    <t>-75.28517333333333</t>
+  </si>
+  <si>
+    <t>25/09/2026 08:30:52</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1075284723_DBD_INGRESO_PDV_22490_25_09_2026_08_30_46.jpg</t>
+  </si>
+  <si>
+    <t>7826199</t>
+  </si>
+  <si>
+    <t>5.3439732</t>
+  </si>
+  <si>
+    <t>-72.3818646</t>
+  </si>
+  <si>
+    <t>25/09/2026 08:40:51</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1073504751_DBD_INGRESO_PDV_11420_25_09_2026_08_40_50.jpg</t>
+  </si>
+  <si>
+    <t>7826201</t>
+  </si>
+  <si>
+    <t>4.6037876</t>
+  </si>
+  <si>
+    <t>-74.1327615</t>
+  </si>
+  <si>
+    <t>25/09/2026 08:41:31</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1124036584_DBD_INGRESO_PDV_45858_25_09_2026_08_41_29.jpg</t>
+  </si>
+  <si>
+    <t>7826209</t>
+  </si>
+  <si>
+    <t>4.806936666666667</t>
+  </si>
+  <si>
+    <t>-75.717295</t>
+  </si>
+  <si>
+    <t>25/09/2026 08:53:48</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1088349837_DBD_INGRESO_PDV_69767_25_09_2026_08_53_46.jpg</t>
+  </si>
+  <si>
+    <t>7826224</t>
+  </si>
+  <si>
+    <t>4.893611666666667</t>
+  </si>
+  <si>
+    <t>-74.03390833333333</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:00:16</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1075688960_DBD_INGRESO_PDV_5879_25_09_2026_09_00_14.jpg</t>
+  </si>
+  <si>
+    <t>7826226</t>
+  </si>
+  <si>
+    <t>10.4145305</t>
+  </si>
+  <si>
+    <t>-75.5298224</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:01:03</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1043635140_DBD_INGRESO_PDV_87085_25_09_2026_09_01_02.jpg</t>
+  </si>
+  <si>
+    <t>7826232</t>
+  </si>
+  <si>
+    <t>7.8861505</t>
+  </si>
+  <si>
+    <t>-72.4934003</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:05:19</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1090436828_DBD_INGRESO_PDV_89546_25_09_2026_09_05_17.jpg</t>
+  </si>
+  <si>
+    <t>7826236</t>
+  </si>
+  <si>
+    <t>10.948263333333333</t>
+  </si>
+  <si>
+    <t>-74.78383833333334</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:06:20</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/72098375_DBD_INGRESO_PDV_77676_25_09_2026_09_06_16.jpg</t>
   </si>
 </sst>
 </file>
@@ -3191,13 +3326,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13795,7 +13931,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG95"/>
+  <dimension ref="A1:AG104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="28.625" bestFit="1" customWidth="1"/>
@@ -20745,6 +20881,707 @@
         <v>43</v>
       </c>
     </row>
+    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A96" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
+      <c r="M96" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q96" s="6" t="s">
+        <v>1039</v>
+      </c>
+      <c r="R96" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="S96" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T96" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="U96" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="V96" s="6"/>
+      <c r="W96" s="6"/>
+      <c r="X96" s="6"/>
+      <c r="Y96" s="6"/>
+      <c r="Z96" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA96" s="6"/>
+      <c r="AB96" s="6"/>
+      <c r="AC96" s="6"/>
+      <c r="AD96" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AE96" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF96" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG96" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A97" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="N97" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q97" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>1045</v>
+      </c>
+      <c r="S97" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T97" s="6" t="s">
+        <v>1046</v>
+      </c>
+      <c r="U97" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V97" s="6"/>
+      <c r="W97" s="6"/>
+      <c r="X97" s="6"/>
+      <c r="Y97" s="6"/>
+      <c r="Z97" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA97" s="6"/>
+      <c r="AB97" s="6"/>
+      <c r="AC97" s="6"/>
+      <c r="AD97" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AE97" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF97" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG97" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q98" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S98" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T98" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="U98" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V98" s="6"/>
+      <c r="W98" s="6"/>
+      <c r="X98" s="6"/>
+      <c r="Y98" s="6"/>
+      <c r="Z98" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA98" s="6"/>
+      <c r="AB98" s="6"/>
+      <c r="AC98" s="6"/>
+      <c r="AD98" s="6" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AE98" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF98" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG98" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A99" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M99" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N99" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="O99" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q99" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R99" s="6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="S99" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T99" s="6" t="s">
+        <v>1056</v>
+      </c>
+      <c r="U99" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V99" s="6"/>
+      <c r="W99" s="6"/>
+      <c r="X99" s="6"/>
+      <c r="Y99" s="6"/>
+      <c r="Z99" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA99" s="6"/>
+      <c r="AB99" s="6"/>
+      <c r="AC99" s="6"/>
+      <c r="AD99" s="6" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AE99" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF99" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG99" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A100" s="6" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q100" s="6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="R100" s="6" t="s">
+        <v>1060</v>
+      </c>
+      <c r="S100" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T100" s="6" t="s">
+        <v>1061</v>
+      </c>
+      <c r="U100" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V100" s="6"/>
+      <c r="W100" s="6"/>
+      <c r="X100" s="6"/>
+      <c r="Y100" s="6"/>
+      <c r="Z100" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA100" s="6"/>
+      <c r="AB100" s="6"/>
+      <c r="AC100" s="6"/>
+      <c r="AD100" s="6" t="s">
+        <v>1062</v>
+      </c>
+      <c r="AE100" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF100" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG100" s="6"/>
+    </row>
+    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A101" s="6" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M101" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="N101" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="O101" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="P101" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q101" s="6" t="s">
+        <v>1064</v>
+      </c>
+      <c r="R101" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="S101" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T101" s="6" t="s">
+        <v>1066</v>
+      </c>
+      <c r="U101" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V101" s="6"/>
+      <c r="W101" s="6"/>
+      <c r="X101" s="6"/>
+      <c r="Y101" s="6"/>
+      <c r="Z101" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA101" s="6"/>
+      <c r="AB101" s="6"/>
+      <c r="AC101" s="6"/>
+      <c r="AD101" s="6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AE101" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF101" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG101" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="O102" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="P102" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q102" s="6" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R102" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="S102" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T102" s="6" t="s">
+        <v>1071</v>
+      </c>
+      <c r="U102" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V102" s="6"/>
+      <c r="W102" s="6"/>
+      <c r="X102" s="6"/>
+      <c r="Y102" s="6"/>
+      <c r="Z102" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA102" s="6"/>
+      <c r="AB102" s="6"/>
+      <c r="AC102" s="6"/>
+      <c r="AD102" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AE102" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF102" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG102" s="6"/>
+    </row>
+    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A103" s="6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M103" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="N103" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="O103" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="P103" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q103" s="6" t="s">
+        <v>1074</v>
+      </c>
+      <c r="R103" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="S103" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T103" s="6" t="s">
+        <v>1076</v>
+      </c>
+      <c r="U103" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V103" s="6"/>
+      <c r="W103" s="6"/>
+      <c r="X103" s="6"/>
+      <c r="Y103" s="6"/>
+      <c r="Z103" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA103" s="6"/>
+      <c r="AB103" s="6"/>
+      <c r="AC103" s="6"/>
+      <c r="AD103" s="6" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AE103" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF103" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG103" s="6"/>
+    </row>
+    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A104" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="O104" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="P104" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q104" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="R104" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="S104" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T104" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="U104" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V104" s="6"/>
+      <c r="W104" s="6"/>
+      <c r="X104" s="6"/>
+      <c r="Y104" s="6"/>
+      <c r="Z104" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA104" s="6"/>
+      <c r="AB104" s="6"/>
+      <c r="AC104" s="6"/>
+      <c r="AD104" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AE104" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF104" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG104" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AG36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5648" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5906" uniqueCount="1143">
   <si>
     <t>ID PDV</t>
   </si>
@@ -3273,6 +3273,186 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/72098375_DBD_INGRESO_PDV_77676_25_09_2026_09_06_16.jpg</t>
+  </si>
+  <si>
+    <t>7826239</t>
+  </si>
+  <si>
+    <t>3.539528333333333</t>
+  </si>
+  <si>
+    <t>-76.31082166666667</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:07:52</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1113649647_DBD_INGRESO_PDV_80967_25_09_2026_09_07_51.jpg</t>
+  </si>
+  <si>
+    <t>7826243</t>
+  </si>
+  <si>
+    <t>4.678328333333333</t>
+  </si>
+  <si>
+    <t>-74.118225</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:09:01</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/80115103_DBD_INGRESO_PDV_25961_25_09_2026_09_09_00.jpg</t>
+  </si>
+  <si>
+    <t>7826244</t>
+  </si>
+  <si>
+    <t>3.368646358139813</t>
+  </si>
+  <si>
+    <t>-76.52757684700191</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:10:13</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1114813506_DBD_INGRESO_PDV_47322_25_09_2026_09_10_12.jpg</t>
+  </si>
+  <si>
+    <t>7826246</t>
+  </si>
+  <si>
+    <t>7.1156637</t>
+  </si>
+  <si>
+    <t>-73.1205635</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:10:46</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1102716954_DBD_INGRESO_PDV_56364_25_09_2026_09_10_45.jpg</t>
+  </si>
+  <si>
+    <t>7826250</t>
+  </si>
+  <si>
+    <t>8.778061666666668</t>
+  </si>
+  <si>
+    <t>-75.86279666666665</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:11:45</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1067881033_DBD_INGRESO_PDV_72049_25_09_2026_09_11_44.jpg</t>
+  </si>
+  <si>
+    <t>7826253</t>
+  </si>
+  <si>
+    <t>4.587621666666666</t>
+  </si>
+  <si>
+    <t>-74.20433833333333</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:13:11</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1014305216_DBD_INGRESO_PDV_58098_25_09_2026_09_13_11.jpg</t>
+  </si>
+  <si>
+    <t>7826277</t>
+  </si>
+  <si>
+    <t>3.472808333333333</t>
+  </si>
+  <si>
+    <t>-76.52852666666666</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:25:30</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/94412336_DBD_INGRESO_PDV_85213_25_09_2026_09_25_29.jpg</t>
+  </si>
+  <si>
+    <t>7826289</t>
+  </si>
+  <si>
+    <t>6.177139</t>
+  </si>
+  <si>
+    <t>-75.5918547</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:34:06</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/71780913_DBD_INGRESO_PDV_86015_25_09_2026_09_34_01.jpg</t>
+  </si>
+  <si>
+    <t>7826299</t>
+  </si>
+  <si>
+    <t>11.015888333333331</t>
+  </si>
+  <si>
+    <t>-74.829795</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:44:48</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/72257237_DBD_INGRESO_PDV_31356_25_09_2026_09_44_47.jpg</t>
+  </si>
+  <si>
+    <t>7826305</t>
+  </si>
+  <si>
+    <t>10.493741666666665</t>
+  </si>
+  <si>
+    <t>-73.26714166666667</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:49:19</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1065626573_DBD_INGRESO_PDV_17609_25_09_2026_09_49_18.jpg</t>
+  </si>
+  <si>
+    <t>7826327</t>
+  </si>
+  <si>
+    <t>4.7302847</t>
+  </si>
+  <si>
+    <t>-74.0330693</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:57:28</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/11225449_DBD_INGRESO_PDV_9829_25_09_2026_09_57_28.jpg</t>
+  </si>
+  <si>
+    <t>7826330</t>
+  </si>
+  <si>
+    <t>11.225453333333332</t>
+  </si>
+  <si>
+    <t>-74.17302666666666</t>
+  </si>
+  <si>
+    <t>25/09/2026 09:59:04</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1110533250_DBD_INGRESO_PDV_28362_25_09_2026_09_59_02.jpg</t>
   </si>
 </sst>
 </file>
@@ -13931,7 +14111,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG104"/>
+  <dimension ref="A1:AG116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="28.625" bestFit="1" customWidth="1"/>
@@ -21582,6 +21762,942 @@
         <v>68</v>
       </c>
     </row>
+    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A105" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M105" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="N105" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="O105" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="P105" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q105" s="6" t="s">
+        <v>1084</v>
+      </c>
+      <c r="R105" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="S105" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T105" s="6" t="s">
+        <v>1086</v>
+      </c>
+      <c r="U105" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V105" s="6"/>
+      <c r="W105" s="6"/>
+      <c r="X105" s="6"/>
+      <c r="Y105" s="6"/>
+      <c r="Z105" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA105" s="6"/>
+      <c r="AB105" s="6"/>
+      <c r="AC105" s="6"/>
+      <c r="AD105" s="6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AE105" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF105" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG105" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A106" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M106" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N106" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="O106" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P106" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q106" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="R106" s="6" t="s">
+        <v>1090</v>
+      </c>
+      <c r="S106" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T106" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="U106" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V106" s="6"/>
+      <c r="W106" s="6"/>
+      <c r="X106" s="6"/>
+      <c r="Y106" s="6"/>
+      <c r="Z106" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA106" s="6"/>
+      <c r="AB106" s="6"/>
+      <c r="AC106" s="6"/>
+      <c r="AD106" s="6" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AE106" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF106" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG106" s="6"/>
+    </row>
+    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A107" s="6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
+      <c r="M107" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="N107" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="O107" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P107" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q107" s="6" t="s">
+        <v>1094</v>
+      </c>
+      <c r="R107" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="S107" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T107" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="U107" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V107" s="6"/>
+      <c r="W107" s="6"/>
+      <c r="X107" s="6"/>
+      <c r="Y107" s="6"/>
+      <c r="Z107" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA107" s="6"/>
+      <c r="AB107" s="6"/>
+      <c r="AC107" s="6"/>
+      <c r="AD107" s="6" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AE107" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF107" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG107" s="6"/>
+    </row>
+    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A108" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="P108" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q108" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="R108" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="S108" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T108" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="U108" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V108" s="6"/>
+      <c r="W108" s="6"/>
+      <c r="X108" s="6"/>
+      <c r="Y108" s="6"/>
+      <c r="Z108" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA108" s="6"/>
+      <c r="AB108" s="6"/>
+      <c r="AC108" s="6"/>
+      <c r="AD108" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AE108" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF108" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG108" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A109" s="6" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M109" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="N109" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="O109" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="P109" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q109" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="R109" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="S109" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T109" s="6" t="s">
+        <v>1106</v>
+      </c>
+      <c r="U109" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V109" s="6"/>
+      <c r="W109" s="6"/>
+      <c r="X109" s="6"/>
+      <c r="Y109" s="6"/>
+      <c r="Z109" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA109" s="6"/>
+      <c r="AB109" s="6"/>
+      <c r="AC109" s="6"/>
+      <c r="AD109" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AE109" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF109" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG109" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A110" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="N110" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="O110" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P110" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q110" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="R110" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="S110" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T110" s="6" t="s">
+        <v>1111</v>
+      </c>
+      <c r="U110" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V110" s="6"/>
+      <c r="W110" s="6"/>
+      <c r="X110" s="6"/>
+      <c r="Y110" s="6"/>
+      <c r="Z110" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA110" s="6"/>
+      <c r="AB110" s="6"/>
+      <c r="AC110" s="6"/>
+      <c r="AD110" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AE110" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF110" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG110" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A111" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M111" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="N111" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="O111" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="P111" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q111" s="6" t="s">
+        <v>1114</v>
+      </c>
+      <c r="R111" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="S111" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T111" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="U111" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V111" s="6"/>
+      <c r="W111" s="6"/>
+      <c r="X111" s="6"/>
+      <c r="Y111" s="6"/>
+      <c r="Z111" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA111" s="6"/>
+      <c r="AB111" s="6"/>
+      <c r="AC111" s="6"/>
+      <c r="AD111" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AE111" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF111" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG111" s="6"/>
+    </row>
+    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A112" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M112" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="N112" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O112" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="P112" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q112" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="R112" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="S112" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T112" s="6" t="s">
+        <v>1121</v>
+      </c>
+      <c r="U112" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V112" s="6"/>
+      <c r="W112" s="6"/>
+      <c r="X112" s="6"/>
+      <c r="Y112" s="6"/>
+      <c r="Z112" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA112" s="6"/>
+      <c r="AB112" s="6"/>
+      <c r="AC112" s="6"/>
+      <c r="AD112" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AE112" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF112" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG112" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A113" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H113" s="6"/>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M113" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="N113" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="O113" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="P113" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q113" s="6" t="s">
+        <v>1124</v>
+      </c>
+      <c r="R113" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="S113" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T113" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="U113" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V113" s="6"/>
+      <c r="W113" s="6"/>
+      <c r="X113" s="6"/>
+      <c r="Y113" s="6"/>
+      <c r="Z113" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA113" s="6"/>
+      <c r="AB113" s="6"/>
+      <c r="AC113" s="6"/>
+      <c r="AD113" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AE113" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF113" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG113" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A114" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H114" s="6"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="6"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="N114" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="O114" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="P114" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q114" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="R114" s="6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="S114" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T114" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="U114" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V114" s="6"/>
+      <c r="W114" s="6"/>
+      <c r="X114" s="6"/>
+      <c r="Y114" s="6"/>
+      <c r="Z114" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA114" s="6"/>
+      <c r="AB114" s="6"/>
+      <c r="AC114" s="6"/>
+      <c r="AD114" s="6" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AE114" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF114" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG114" s="6"/>
+    </row>
+    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A115" s="6" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6"/>
+      <c r="L115" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M115" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N115" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="O115" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="P115" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q115" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="R115" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="S115" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T115" s="6" t="s">
+        <v>1136</v>
+      </c>
+      <c r="U115" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V115" s="6"/>
+      <c r="W115" s="6"/>
+      <c r="X115" s="6"/>
+      <c r="Y115" s="6"/>
+      <c r="Z115" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA115" s="6"/>
+      <c r="AB115" s="6"/>
+      <c r="AC115" s="6"/>
+      <c r="AD115" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AE115" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF115" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG115" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A116" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
+      <c r="K116" s="6"/>
+      <c r="L116" s="6"/>
+      <c r="M116" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="N116" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O116" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="P116" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q116" s="6" t="s">
+        <v>1139</v>
+      </c>
+      <c r="R116" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="S116" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T116" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="U116" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V116" s="6"/>
+      <c r="W116" s="6"/>
+      <c r="X116" s="6"/>
+      <c r="Y116" s="6"/>
+      <c r="Z116" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA116" s="6"/>
+      <c r="AB116" s="6"/>
+      <c r="AC116" s="6"/>
+      <c r="AD116" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="AE116" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF116" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG116" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AG36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5906" uniqueCount="1143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6056" uniqueCount="1181">
   <si>
     <t>ID PDV</t>
   </si>
@@ -3453,6 +3453,120 @@
   </si>
   <si>
     <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1110533250_DBD_INGRESO_PDV_28362_25_09_2026_09_59_02.jpg</t>
+  </si>
+  <si>
+    <t>7826332</t>
+  </si>
+  <si>
+    <t>4.755941</t>
+  </si>
+  <si>
+    <t>-74.0466921</t>
+  </si>
+  <si>
+    <t>25/09/2026 10:00:09</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1233490257_DBD_INGRESO_PDV_15459_25_09_2026_10_00_07.jpg</t>
+  </si>
+  <si>
+    <t>7826334</t>
+  </si>
+  <si>
+    <t>4.7009855</t>
+  </si>
+  <si>
+    <t>-74.2307378</t>
+  </si>
+  <si>
+    <t>25/09/2026 10:01:09</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1070464010_DBD_INGRESO_PDV_60017_25_09_2026_10_01_08.jpg</t>
+  </si>
+  <si>
+    <t>7826351</t>
+  </si>
+  <si>
+    <t>4.61997811</t>
+  </si>
+  <si>
+    <t>-74.08501256</t>
+  </si>
+  <si>
+    <t>25/09/2026 10:08:48</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1001277768_DBD_INGRESO_PDV_34599_25_09_2026_10_08_05.jpg</t>
+  </si>
+  <si>
+    <t>7826396</t>
+  </si>
+  <si>
+    <t>27057</t>
+  </si>
+  <si>
+    <t>Homecenter Rio Negro</t>
+  </si>
+  <si>
+    <t>6.1467638</t>
+  </si>
+  <si>
+    <t>-75.377237</t>
+  </si>
+  <si>
+    <t>25/09/2026 10:39:06</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1039448347_DBD_INGRESO_PDV_51788_25_09_2026_10_39_05.jpg</t>
+  </si>
+  <si>
+    <t>7826399</t>
+  </si>
+  <si>
+    <t>10.3833184</t>
+  </si>
+  <si>
+    <t>-75.4686525</t>
+  </si>
+  <si>
+    <t>25/09/2026 10:42:03</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1002247264_DBD_INGRESO_PDV_83368_25_09_2026_10_42_02.jpg</t>
+  </si>
+  <si>
+    <t>7826443</t>
+  </si>
+  <si>
+    <t>4.685019</t>
+  </si>
+  <si>
+    <t>-74.0792244</t>
+  </si>
+  <si>
+    <t>25/09/2026 10:59:38</t>
+  </si>
+  <si>
+    <t>0h 30m</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1028865500_DBD_INGRESO_PDV_73611_25_09_2026_10_59_38.jpg</t>
+  </si>
+  <si>
+    <t>7826482</t>
+  </si>
+  <si>
+    <t>4.7559901</t>
+  </si>
+  <si>
+    <t>-74.046487</t>
+  </si>
+  <si>
+    <t>25/09/2026 11:13:29</t>
+  </si>
+  <si>
+    <t>https://dbdplus.accionplus.com/dbdPlus2/webMod/Public/imagenesDBD/4714/77/1007627363_DBD_INGRESO_PDV_55475_25_09_2026_11_13_27.jpg</t>
   </si>
 </sst>
 </file>
@@ -14111,7 +14225,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG116"/>
+  <dimension ref="A1:AG123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="28.625" bestFit="1" customWidth="1"/>
@@ -22698,6 +22812,551 @@
         <v>68</v>
       </c>
     </row>
+    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A117" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H117" s="6"/>
+      <c r="I117" s="6"/>
+      <c r="J117" s="6"/>
+      <c r="K117" s="6"/>
+      <c r="L117" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M117" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N117" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O117" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="P117" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q117" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="R117" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="S117" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T117" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="U117" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V117" s="6"/>
+      <c r="W117" s="6"/>
+      <c r="X117" s="6"/>
+      <c r="Y117" s="6"/>
+      <c r="Z117" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA117" s="6"/>
+      <c r="AB117" s="6"/>
+      <c r="AC117" s="6"/>
+      <c r="AD117" s="6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AE117" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF117" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG117" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A118" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H118" s="6"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="6"/>
+      <c r="K118" s="6"/>
+      <c r="L118" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M118" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="N118" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="O118" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P118" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q118" s="6" t="s">
+        <v>1149</v>
+      </c>
+      <c r="R118" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="S118" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T118" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="U118" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V118" s="6"/>
+      <c r="W118" s="6"/>
+      <c r="X118" s="6"/>
+      <c r="Y118" s="6"/>
+      <c r="Z118" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA118" s="6"/>
+      <c r="AB118" s="6"/>
+      <c r="AC118" s="6"/>
+      <c r="AD118" s="6" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AE118" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF118" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG118" s="6"/>
+    </row>
+    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A119" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="6"/>
+      <c r="K119" s="6"/>
+      <c r="L119" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M119" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N119" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="O119" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="P119" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q119" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="R119" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="S119" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T119" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="U119" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V119" s="6"/>
+      <c r="W119" s="6"/>
+      <c r="X119" s="6"/>
+      <c r="Y119" s="6"/>
+      <c r="Z119" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA119" s="6"/>
+      <c r="AB119" s="6"/>
+      <c r="AC119" s="6"/>
+      <c r="AD119" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AE119" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF119" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG119" s="6"/>
+    </row>
+    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A120" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H120" s="6"/>
+      <c r="I120" s="6"/>
+      <c r="J120" s="6"/>
+      <c r="K120" s="6"/>
+      <c r="L120" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M120" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="N120" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="O120" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P120" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q120" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="R120" s="6" t="s">
+        <v>1162</v>
+      </c>
+      <c r="S120" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T120" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="U120" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V120" s="6"/>
+      <c r="W120" s="6"/>
+      <c r="X120" s="6"/>
+      <c r="Y120" s="6"/>
+      <c r="Z120" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA120" s="6"/>
+      <c r="AB120" s="6"/>
+      <c r="AC120" s="6"/>
+      <c r="AD120" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AE120" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF120" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG120" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A121" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H121" s="6"/>
+      <c r="I121" s="6"/>
+      <c r="J121" s="6"/>
+      <c r="K121" s="6"/>
+      <c r="L121" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M121" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N121" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="O121" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P121" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q121" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="R121" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="S121" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T121" s="6" t="s">
+        <v>1168</v>
+      </c>
+      <c r="U121" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V121" s="6"/>
+      <c r="W121" s="6"/>
+      <c r="X121" s="6"/>
+      <c r="Y121" s="6"/>
+      <c r="Z121" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA121" s="6"/>
+      <c r="AB121" s="6"/>
+      <c r="AC121" s="6"/>
+      <c r="AD121" s="6" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AE121" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF121" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG121" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A122" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H122" s="6"/>
+      <c r="I122" s="6"/>
+      <c r="J122" s="6"/>
+      <c r="K122" s="6"/>
+      <c r="L122" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M122" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N122" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O122" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P122" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q122" s="6" t="s">
+        <v>1171</v>
+      </c>
+      <c r="R122" s="6" t="s">
+        <v>1172</v>
+      </c>
+      <c r="S122" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T122" s="6" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U122" s="6" t="s">
+        <v>1174</v>
+      </c>
+      <c r="V122" s="6"/>
+      <c r="W122" s="6"/>
+      <c r="X122" s="6"/>
+      <c r="Y122" s="6"/>
+      <c r="Z122" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA122" s="6"/>
+      <c r="AB122" s="6"/>
+      <c r="AC122" s="6"/>
+      <c r="AD122" s="6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="AE122" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF122" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG122" s="6"/>
+    </row>
+    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A123" s="6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H123" s="6"/>
+      <c r="I123" s="6"/>
+      <c r="J123" s="6"/>
+      <c r="K123" s="6"/>
+      <c r="L123" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M123" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N123" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="O123" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="P123" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q123" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="R123" s="6" t="s">
+        <v>1178</v>
+      </c>
+      <c r="S123" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="T123" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="U123" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="V123" s="6"/>
+      <c r="W123" s="6"/>
+      <c r="X123" s="6"/>
+      <c r="Y123" s="6"/>
+      <c r="Z123" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA123" s="6"/>
+      <c r="AB123" s="6"/>
+      <c r="AC123" s="6"/>
+      <c r="AD123" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="AE123" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF123" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG123" s="6"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AG36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/reporte_ingresos.xlsx
+++ b/data/reporte_ingresos.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="programacion" sheetId="1" r:id="rId1"/>
@@ -11343,11 +11343,11 @@
       </c>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>61</v>
+      <c r="A108" s="6" t="s">
+        <v>302</v>
       </c>
       <c r="B108" t="s">
-        <v>62</v>
+        <v>303</v>
       </c>
       <c r="C108" t="s">
         <v>63</v>
@@ -11745,11 +11745,11 @@
       </c>
     </row>
     <row r="114" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>77</v>
-      </c>
-      <c r="B114" t="s">
-        <v>78</v>
+      <c r="A114" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>1160</v>
       </c>
       <c r="C114" t="s">
         <v>79</v>
